--- a/tame_output/ON/bt/strategyON_20240621.xlsx
+++ b/tame_output/ON/bt/strategyON_20240621.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-567.0%</t>
+          <t>-566.9%</t>
         </is>
       </c>
     </row>
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.83085507417388</v>
+        <v>3.830855074173881</v>
       </c>
       <c r="C2001" t="n">
         <v>3.417095481377384</v>
       </c>
       <c r="D2001" t="n">
-        <v>-4.053969619412668</v>
+        <v>-4.053625267226006</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.795151209298569</v>
+        <v>1.795288950173234</v>
       </c>
       <c r="F2001" t="n">
-        <v>-0.00852802849177714</v>
+        <v>-0.008183676305114684</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.411978664282318</v>
+        <v>3.412185275594315</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240621.xlsx
+++ b/tame_output/ON/bt/strategyON_20240621.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.4%</t>
+          <t>-75.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.1%</t>
+          <t>94.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.9%</t>
+          <t>-70.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.2%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-566.9%</t>
+          <t>-560.2%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-196.7%</t>
+          <t>-194.0%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-23.0%</t>
+          <t>-22.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-15.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-193.6%</t>
+          <t>-191.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-224.8%</t>
+          <t>-218.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-104.8%</t>
+          <t>-100.8%</t>
         </is>
       </c>
     </row>
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.830855074173881</v>
+        <v>3.83085507417388</v>
       </c>
       <c r="C2001" t="n">
         <v>3.417095481377384</v>
       </c>
       <c r="D2001" t="n">
-        <v>-4.053625267226006</v>
+        <v>-3.986184625703793</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.795288950173234</v>
+        <v>1.822265206782119</v>
       </c>
       <c r="F2001" t="n">
-        <v>-0.008183676305114684</v>
+        <v>0.059256965217098</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.412185275594315</v>
+        <v>3.452649660507643</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240621.xlsx
+++ b/tame_output/ON/bt/strategyON_20240621.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>74.0%</t>
+          <t>76.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>38.9%</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.7%</t>
+          <t>123.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-100.8%</t>
+          <t>-96.2%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2001"/>
+  <dimension ref="A1:G2002"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46993,7 +46993,7 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024966</v>
+        <v>3.836023391024965</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
@@ -47568,7 +47568,7 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.83085507417388</v>
+        <v>3.769472653557221</v>
       </c>
       <c r="C2001" t="n">
         <v>3.417095481377384</v>
@@ -47584,6 +47584,29 @@
       </c>
       <c r="G2001" t="n">
         <v>3.452649660507643</v>
+      </c>
+    </row>
+    <row r="2002">
+      <c r="A2002" s="2" t="n">
+        <v>45464</v>
+      </c>
+      <c r="B2002" t="n">
+        <v>3.831505808535466</v>
+      </c>
+      <c r="C2002" t="n">
+        <v>3.505313519128397</v>
+      </c>
+      <c r="D2002" t="n">
+        <v>-3.986184625703793</v>
+      </c>
+      <c r="E2002" t="n">
+        <v>1.822265206782119</v>
+      </c>
+      <c r="F2002" t="n">
+        <v>0.059256965217098</v>
+      </c>
+      <c r="G2002" t="n">
+        <v>3.498377316114765</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240621.xlsx
+++ b/tame_output/ON/bt/strategyON_20240621.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>29.0%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>71.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,32 +849,32 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>22.7%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.1%</t>
+          <t>-75.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.1%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.6%</t>
+          <t>123.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.0%</t>
+          <t>94.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.6%</t>
+          <t>-71.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>455.0%</t>
+          <t>451.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-560.2%</t>
+          <t>-563.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-47.4%</t>
+          <t>-47.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-194.0%</t>
+          <t>-189.8%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-22.0%</t>
+          <t>-23.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-15.1%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-191.3%</t>
+          <t>-185.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-218.1%</t>
+          <t>-224.9%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-96.2%</t>
+          <t>-112.4%</t>
         </is>
       </c>
     </row>
@@ -43681,7 +43681,7 @@
         <v>45294</v>
       </c>
       <c r="B1832" t="n">
-        <v>3.301413393085799</v>
+        <v>3.301413393085798</v>
       </c>
       <c r="C1832" t="n">
         <v>3.130069279090508</v>
@@ -43704,7 +43704,7 @@
         <v>45295</v>
       </c>
       <c r="B1833" t="n">
-        <v>3.311607601705545</v>
+        <v>3.311607601705544</v>
       </c>
       <c r="C1833" t="n">
         <v>3.12694133299222</v>
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045693</v>
+        <v>3.317575502045692</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355689</v>
+        <v>3.311888301355688</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279813</v>
+        <v>3.385382209279812</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511403</v>
+        <v>3.367379938511402</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386092</v>
+        <v>3.376932391386091</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998559</v>
+        <v>3.367370539998558</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082123</v>
+        <v>3.299560092082122</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757922</v>
+        <v>3.293490533757921</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.29376671976074</v>
+        <v>3.293766719760739</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201486</v>
+        <v>3.295507330201485</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153005</v>
+        <v>3.258791981153004</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382191</v>
+        <v>3.27276013138219</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074623</v>
+        <v>3.251475576074622</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213495</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416044</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.235981977382327</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495498</v>
+        <v>3.278199702495497</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178242</v>
+        <v>3.315884374178241</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207809</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310978</v>
+        <v>3.284619513310977</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330521</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108638</v>
+        <v>3.305023265108637</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.34137872309782</v>
+        <v>3.341378723097819</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094115</v>
+        <v>3.374439043094114</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199284</v>
+        <v>3.405960511199283</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969592</v>
+        <v>3.424633354969591</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923085</v>
+        <v>3.419979433923084</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297748</v>
+        <v>3.458100091297747</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317616</v>
+        <v>3.447750501317615</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.50351550673717</v>
+        <v>3.503515506737169</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341313</v>
+        <v>3.503170282341312</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539463</v>
+        <v>3.501052558539462</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937496</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141699</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.48587859441027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940719</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67684154977058</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.768951674611567</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -46651,19 +46651,19 @@
         <v>3.705571661815456</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.694396870355521</v>
+        <v>2.753410111293847</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.748085457255398</v>
+        <v>-4.788624329075721</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7948062631396149</v>
+        <v>0.8376039553498111</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.2896107876403166</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.520630397771332</v>
+        <v>2.579643638709657</v>
       </c>
     </row>
     <row r="1962">
@@ -46674,19 +46674,19 @@
         <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.690921589563766</v>
+        <v>2.749934830502092</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.7290473295481</v>
+        <v>-4.769586201368424</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7989462334307786</v>
+        <v>0.8417439256409749</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.3477943989715111</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.48224495018086</v>
+        <v>2.541258191119185</v>
       </c>
     </row>
     <row r="1963">
@@ -46697,19 +46697,19 @@
         <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.868503458502447</v>
+        <v>2.927516699440772</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.760173960698719</v>
+        <v>-4.800712832519042</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.964077449909212</v>
+        <v>1.006875142119408</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.3477943989715111</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.65982681911954</v>
+        <v>2.718840060057866</v>
       </c>
     </row>
     <row r="1964">
@@ -46720,19 +46720,19 @@
         <v>3.722447362067867</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.86933678748858</v>
+        <v>2.928350028426906</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.774040722032637</v>
+        <v>-4.81457959385296</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9593640743617784</v>
+        <v>1.002161766571974</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.385652315705334</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.63794539806538</v>
+        <v>2.696958639003705</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.787425580789124</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.875345317885506</v>
+        <v>2.934358558823832</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.794298020561595</v>
+        <v>-4.834836892381918</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.957269685347121</v>
+        <v>1.000067377557317</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.385652315705334</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.643953928462306</v>
+        <v>2.702967169400631</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.781501250519911</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.954497965677528</v>
+        <v>3.013511206615854</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.646555050326592</v>
+        <v>-4.687093922146915</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.095519521233144</v>
+        <v>1.13831721344334</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.2178449584704509</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.823790990595258</v>
+        <v>2.882804231533584</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.802245929181173</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.957291587209009</v>
+        <v>3.016304828147335</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.748569732857813</v>
+        <v>-4.789108604678137</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.057507269752136</v>
+        <v>1.100304961962333</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.2178449584704509</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.826584612126739</v>
+        <v>2.885597853065065</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394734</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.957953935600667</v>
+        <v>3.016967176538993</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.742417026805029</v>
+        <v>-4.782955898625352</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.060630700564908</v>
+        <v>1.103428392775105</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.2116922524176666</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.830938584150068</v>
+        <v>2.889951825088393</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.957034412340778</v>
+        <v>3.016047653279103</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.759226324955531</v>
+        <v>-4.799765196775854</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.052987458044818</v>
+        <v>1.095785150255014</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.2285015505681682</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.819933481999877</v>
+        <v>2.878946722938203</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.023369966137599</v>
+        <v>3.082383207075924</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.696928326179409</v>
+        <v>-4.737467197999732</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.144242211352088</v>
+        <v>1.187039903562284</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.2285015505681682</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.886269035796698</v>
+        <v>2.945282276735024</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992194</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.731950838526997</v>
+        <v>2.790964079465322</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.495138128514251</v>
+        <v>-4.535677000334574</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9335391628075491</v>
+        <v>0.9763368550177454</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.03048335839901384</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.713660823487589</v>
+        <v>2.772674064425914</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.802241070849172</v>
+        <v>2.861254311787497</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.435247446871657</v>
+        <v>-4.475786318691981</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.027785667786762</v>
+        <v>1.070583359996958</v>
       </c>
       <c r="F1972" t="n">
         <v>0.02940732324357964</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.81988546479532</v>
+        <v>2.878898705733645</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319549</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.816868806965215</v>
+        <v>2.875882047903541</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.532987991496632</v>
+        <v>-4.573526863316955</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.003317186052815</v>
+        <v>1.046114878263012</v>
       </c>
       <c r="F1973" t="n">
         <v>0.01351804511059945</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.824979634031576</v>
+        <v>2.883992874969901</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489388</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.815404787789887</v>
+        <v>2.874418028728213</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.709325751619561</v>
+        <v>-4.749864623439884</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9313180628283155</v>
+        <v>0.9741157550385116</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.1628197150123299</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.71771295878249</v>
+        <v>2.776726199720815</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397798</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.813896405829816</v>
+        <v>2.872909646768141</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.632903705187634</v>
+        <v>-4.673442577007958</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9603784994410147</v>
+        <v>1.003176191651211</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.1628197150123299</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.716204576822418</v>
+        <v>2.775217817760744</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024965</v>
+        <v>3.833513460316253</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.813759273265252</v>
+        <v>2.872772514203577</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.588530573549066</v>
+        <v>-4.629069445369389</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9779906195318784</v>
+        <v>1.020788311742075</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.1184465833737613</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.742691323240996</v>
+        <v>2.801704564179321</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863226</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.813759273265252</v>
+        <v>2.867166308342168</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.580576603254293</v>
+        <v>-4.540915233630213</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9811722076497873</v>
+        <v>1.050443790576336</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.1184465833737613</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.742691323240996</v>
+        <v>2.796098358317912</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947585</v>
+        <v>3.833011148190325</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.820141030293057</v>
+        <v>2.873548065369972</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.532920872693238</v>
+        <v>-4.493259503069157</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.006616256902014</v>
+        <v>1.075887839828562</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.0707908528127057</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.777666518605433</v>
+        <v>2.831073553682349</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326877</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.825033403667781</v>
+        <v>2.878440438744697</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.405236562898941</v>
+        <v>-4.365575193274861</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.062582354194458</v>
+        <v>1.131853937121005</v>
       </c>
       <c r="F1979" t="n">
         <v>0.05689345698159076</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.859169477856736</v>
+        <v>2.912576512933652</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314553</v>
+        <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.811788076143654</v>
+        <v>2.865195111220569</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.46590315330133</v>
+        <v>-4.42624178367725</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.025070390509374</v>
+        <v>1.094341973435922</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.02480485973694291</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.796905160301488</v>
+        <v>2.850312195378404</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690029</v>
+        <v>3.816837033932769</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.815885778754282</v>
+        <v>2.869292813831198</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.421064751692931</v>
+        <v>-4.381403382068852</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.047103453763362</v>
+        <v>1.11637503668991</v>
       </c>
       <c r="F1981" t="n">
         <v>-0.02026142679207343</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.803728922679039</v>
+        <v>2.857135957755954</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674313</v>
+        <v>3.817932354917053</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.82004671838536</v>
+        <v>2.873453753462276</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.521823387449929</v>
+        <v>-4.48216201782585</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.010960939091641</v>
+        <v>1.080232522018189</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.1090869955190789</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.754594521073913</v>
+        <v>2.808001556150828</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163222</v>
+        <v>3.826684745405962</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.825926320913197</v>
+        <v>2.879333355990113</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.477620550364029</v>
+        <v>-4.437959180739949</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.034521676453839</v>
+        <v>1.103793259380386</v>
       </c>
       <c r="F1983" t="n">
         <v>-0.06488415843317841</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.78699582585329</v>
+        <v>2.840402860930206</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022907</v>
+        <v>3.838199629265647</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.824336321382445</v>
+        <v>2.87774335645936</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.514599578027472</v>
+        <v>-4.474938208403392</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.018140065857709</v>
+        <v>1.087411648784256</v>
       </c>
       <c r="F1984" t="n">
         <v>-0.02791025664184787</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.807590167397336</v>
+        <v>2.860997202474252</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042141</v>
+        <v>3.863895080284881</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.875584086565484</v>
+        <v>2.9289911216424</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.534657656892312</v>
+        <v>-4.494996287268233</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.061364599494812</v>
+        <v>1.13063618242136</v>
       </c>
       <c r="F1985" t="n">
         <v>-0.02791025664184787</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.858837932580376</v>
+        <v>2.912244967657291</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078284</v>
+        <v>3.865338681321024</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.874024791159738</v>
+        <v>2.927431826236653</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.494726983714422</v>
+        <v>-4.455065614090342</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.075777573360222</v>
+        <v>1.145049156286769</v>
       </c>
       <c r="F1986" t="n">
         <v>0.01202041653604247</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.881237041081363</v>
+        <v>2.934644076158279</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232401</v>
+        <v>3.864489842475141</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.868973019398008</v>
+        <v>2.922380054474923</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.443694890991894</v>
+        <v>-4.404033521367815</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.091138638687503</v>
+        <v>1.16041022161405</v>
       </c>
       <c r="F1987" t="n">
         <v>0.06305250925857042</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.90680452495315</v>
+        <v>2.960211560030066</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162116</v>
+        <v>3.842547360404857</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.886160423490713</v>
+        <v>2.939567458567628</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.378470709864689</v>
+        <v>-4.338809340240609</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.13441571523109</v>
+        <v>1.203687298157637</v>
       </c>
       <c r="F1988" t="n">
         <v>0.128276690385776</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.963126437722178</v>
+        <v>3.016533472799094</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.84009022063982</v>
+        <v>3.84006118688256</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.882121395789993</v>
+        <v>2.935528430866909</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.341043689793555</v>
+        <v>-4.301382320169475</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.145347495558824</v>
+        <v>1.214619078485371</v>
       </c>
       <c r="F1989" t="n">
         <v>0.1335282284149577</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.962238332838968</v>
+        <v>3.015645367915883</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749925</v>
+        <v>3.845169808992665</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.883378188121233</v>
+        <v>2.936785223198149</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.361155345828263</v>
+        <v>-4.321493976204184</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.138559625476181</v>
+        <v>1.207831208402728</v>
       </c>
       <c r="F1990" t="n">
         <v>0.1445555734123769</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.97011153216866</v>
+        <v>3.023518567245575</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393551</v>
+        <v>3.828661445636292</v>
       </c>
       <c r="C1991" t="n">
-        <v>3.043935959142444</v>
+        <v>3.09734299421936</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.307410531401058</v>
+        <v>-4.267749161776979</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.320615322268273</v>
+        <v>1.389886905194821</v>
       </c>
       <c r="F1991" t="n">
         <v>0.1546188828528389</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.136707288854148</v>
+        <v>3.190114323931063</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714889</v>
+        <v>3.81322282095763</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.164048868360261</v>
+        <v>3.217455903437177</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.283618962794916</v>
+        <v>-4.243957593170837</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.450244858928547</v>
+        <v>1.519516441855095</v>
       </c>
       <c r="F1992" t="n">
         <v>0.1784104514589812</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.27109513923565</v>
+        <v>3.324502174312566</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756015</v>
+        <v>3.814230727998755</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.15575684437412</v>
+        <v>3.209163879451036</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.257534878531108</v>
+        <v>-4.217873508907029</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.45238646864793</v>
+        <v>1.521658051574477</v>
       </c>
       <c r="F1993" t="n">
         <v>0.1784104514589812</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.262803115249509</v>
+        <v>3.316210150326425</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654189</v>
+        <v>3.803397818896929</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.1539500399579</v>
+        <v>3.207357075034815</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.25320057547406</v>
+        <v>-4.213539205849981</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.452313385454528</v>
+        <v>1.521584968381076</v>
       </c>
       <c r="F1994" t="n">
         <v>0.3300605547781851</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.351986372824811</v>
+        <v>3.405393407901727</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.79629317771712</v>
+        <v>3.79626414395986</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.171504445684691</v>
+        <v>3.224911480761607</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.244308114080777</v>
+        <v>-4.204646744456698</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.473424775738633</v>
+        <v>1.54269635866518</v>
       </c>
       <c r="F1995" t="n">
         <v>0.3300605547781851</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.369540778551603</v>
+        <v>3.422947813628518</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702628</v>
+        <v>3.794424941945368</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.163359493089275</v>
+        <v>3.216766528166191</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.412784231050654</v>
+        <v>-4.373122861426575</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.397889376355266</v>
+        <v>1.467160959281813</v>
       </c>
       <c r="F1996" t="n">
         <v>0.3021127190616043</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.344627124526238</v>
+        <v>3.398034159603153</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795603100539971</v>
+        <v>3.795574066782711</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.233772154546119</v>
+        <v>3.287179189623034</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.714984702189071</v>
+        <v>-3.675323332564992</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.747421849356743</v>
+        <v>1.81669343228329</v>
       </c>
       <c r="F1997" t="n">
         <v>0.2317646596911936</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.372830950360835</v>
+        <v>3.42623798543775</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784700379389901</v>
+        <v>3.784671345632641</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.224436177043023</v>
+        <v>3.277843212119939</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.692263598505919</v>
+        <v>-3.652602228881839</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.747174313326908</v>
+        <v>1.816445896253456</v>
       </c>
       <c r="F1998" t="n">
         <v>0.2317646596911936</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.363494972857739</v>
+        <v>3.416902007934655</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783234730534939</v>
+        <v>3.783205696777679</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.383342302894192</v>
+        <v>3.436749337971108</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.832556198043111</v>
+        <v>-3.792894828419032</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.849963399363201</v>
+        <v>1.919234982289748</v>
       </c>
       <c r="F1999" t="n">
         <v>0.09147206015400094</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.438225538986593</v>
+        <v>3.491632574063509</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779962759401677</v>
+        <v>3.779933725644417</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.420420125387839</v>
+        <v>3.473827160464754</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.987337204821366</v>
+        <v>-3.947675835197287</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.825128819145545</v>
+        <v>1.894400402072092</v>
       </c>
       <c r="F2000" t="n">
         <v>0.05810438609952484</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.455282757047554</v>
+        <v>3.50868979212447</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769472653557221</v>
+        <v>3.773644570866075</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.417095481377384</v>
+        <v>3.4705025164543</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.986184625703793</v>
+        <v>-4.014936279219204</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.822265206782119</v>
+        <v>1.864171580452871</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.059256965217098</v>
+        <v>-0.009156057922392269</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.452649660507643</v>
+        <v>3.465008881700864</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.831505808535466</v>
+        <v>3.570844818288085</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.505313519128397</v>
+        <v>3.34319605937123</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.986184625703793</v>
+        <v>-4.014936279219204</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.822265206782119</v>
+        <v>1.864171580452871</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.059256965217098</v>
+        <v>-0.009156057922392269</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.498377316114765</v>
+        <v>3.336259856357597</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240621.xlsx
+++ b/tame_output/ON/bt/strategyON_20240621.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>62.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>56.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>71.3%</t>
+          <t>76.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,32 +849,32 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>39.2%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.2%</t>
+          <t>-74.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>108.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.5%</t>
+          <t>123.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.6%</t>
+          <t>-51.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.1%</t>
+          <t>-69.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>451.2%</t>
+          <t>455.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-563.1%</t>
+          <t>-543.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.2%</t>
+          <t>-39.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-47.8%</t>
+          <t>-29.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-189.8%</t>
+          <t>-187.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-23.0%</t>
+          <t>-22.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-15.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-185.7%</t>
+          <t>-194.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-224.9%</t>
+          <t>-218.2%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-112.4%</t>
+          <t>-95.9%</t>
         </is>
       </c>
     </row>
@@ -43681,7 +43681,7 @@
         <v>45294</v>
       </c>
       <c r="B1832" t="n">
-        <v>3.301413393085798</v>
+        <v>3.301413393085799</v>
       </c>
       <c r="C1832" t="n">
         <v>3.130069279090508</v>
@@ -43704,7 +43704,7 @@
         <v>45295</v>
       </c>
       <c r="B1833" t="n">
-        <v>3.311607601705544</v>
+        <v>3.311607601705545</v>
       </c>
       <c r="C1833" t="n">
         <v>3.12694133299222</v>
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045692</v>
+        <v>3.317575502045693</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355688</v>
+        <v>3.311888301355689</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279812</v>
+        <v>3.385382209279813</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511402</v>
+        <v>3.367379938511403</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386091</v>
+        <v>3.376932391386092</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998558</v>
+        <v>3.367370539998559</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082122</v>
+        <v>3.299560092082123</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757921</v>
+        <v>3.293490533757922</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760739</v>
+        <v>3.29376671976074</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201485</v>
+        <v>3.295507330201486</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153004</v>
+        <v>3.258791981153005</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.27276013138219</v>
+        <v>3.272760131382191</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074622</v>
+        <v>3.251475576074623</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213495</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416044</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382327</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495497</v>
+        <v>3.278199702495498</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178241</v>
+        <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207809</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310977</v>
+        <v>3.284619513310978</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330521</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108637</v>
+        <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097819</v>
+        <v>3.34137872309782</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094114</v>
+        <v>3.374439043094115</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199283</v>
+        <v>3.405960511199284</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969591</v>
+        <v>3.424633354969592</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923084</v>
+        <v>3.419979433923085</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297747</v>
+        <v>3.458100091297748</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317615</v>
+        <v>3.447750501317616</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737169</v>
+        <v>3.50351550673717</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341312</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539462</v>
+        <v>3.501052558539463</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937496</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141699</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.902814325123623</v>
+        <v>-9.76197020833151</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8211620621079496</v>
+        <v>-0.7648244153911046</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.221921394571273</v>
+        <v>-2.215858085819809</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.807167255512484</v>
+        <v>1.810805240763362</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.977147301383788</v>
+        <v>-9.836303184591674</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8464126981275792</v>
+        <v>-0.7900750514107342</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.366620918505946</v>
+        <v>-2.360557609754482</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.724830095636116</v>
+        <v>1.728468080886994</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440632</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.903677469716339</v>
+        <v>-9.762833352924225</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8016530639671786</v>
+        <v>-0.7453154172503336</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.293151086838497</v>
+        <v>-2.287087778087033</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.784283696130006</v>
+        <v>1.787921681380885</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.07880188710288</v>
+        <v>-9.937957770310769</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8571476101742794</v>
+        <v>-0.8008099634574339</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.468275504225041</v>
+        <v>-2.462212195473577</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.693764266445597</v>
+        <v>1.697402251696475</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587859441027</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.31325398111737</v>
+        <v>-10.17240986432526</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9581476126816715</v>
+        <v>-0.901809965964826</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.468275504225041</v>
+        <v>-2.462212195473577</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.686545101544001</v>
+        <v>1.690183086794879</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.41762871214382</v>
+        <v>-10.2767845953517</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.006569695866226</v>
+        <v>-0.9502320491493808</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.572650235251487</v>
+        <v>-2.566586926500023</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.617248072154157</v>
+        <v>1.620886057405035</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390584</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.47041486774414</v>
+        <v>-10.32957075095203</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.0265683682678</v>
+        <v>-0.9702307215509549</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.668325721833884</v>
+        <v>-2.66226241308242</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.560958570043275</v>
+        <v>1.564596555294153</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.59645166111243</v>
+        <v>-10.45560754432032</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.074289356986001</v>
+        <v>-1.017951710269156</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.643074099024141</v>
+        <v>-2.637010790272678</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.578803272358235</v>
+        <v>1.582441257609114</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.54443614714362</v>
+        <v>-10.40359203035151</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.049492815712076</v>
+        <v>-0.99315516899523</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.643074099024141</v>
+        <v>-2.637010790272678</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.582793608044636</v>
+        <v>1.586431593295514</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.68610798886774</v>
+        <v>-10.54526387207563</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.107636779300465</v>
+        <v>-1.05129913258362</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.643074099024141</v>
+        <v>-2.637010790272678</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.581318381145894</v>
+        <v>1.584956366396773</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.63651714444291</v>
+        <v>-10.49567302765079</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.072747031365659</v>
+        <v>-1.016409384648814</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.593483254599307</v>
+        <v>-2.587419945847844</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.626126297965667</v>
+        <v>1.629764283216545</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.62370975143813</v>
+        <v>-10.48286563464602</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.080675207810433</v>
+        <v>-1.024337561093587</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.642339029608209</v>
+        <v>-2.636275720856745</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.583761699313643</v>
+        <v>1.587399684564522</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.39786459871872</v>
+        <v>-10.25702048192661</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.9807580736864598</v>
+        <v>-0.9244204269696144</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.600412354021045</v>
+        <v>-2.594349045269581</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.61849677770215</v>
+        <v>1.622134762953028</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.27328594238113</v>
+        <v>-10.13244182558902</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9297874665953638</v>
+        <v>-0.8734498198785183</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.600412354021045</v>
+        <v>-2.594349045269581</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.619635922258209</v>
+        <v>1.623273907509087</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646215</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.32618123042542</v>
+        <v>-10.1853371136333</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9483118076509713</v>
+        <v>-0.8919741609341258</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.595457007932599</v>
+        <v>-2.589393699181135</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.625242904073384</v>
+        <v>1.628880889324263</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611567</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.25404805513754</v>
+        <v>-10.11320393834542</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9137248332971817</v>
+        <v>-0.8573871865803371</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.595457007932599</v>
+        <v>-2.589393699181135</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.630976608312021</v>
+        <v>1.634614593562899</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.18268166252789</v>
+        <v>-10.04183754573578</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8949155386471883</v>
+        <v>-0.8385778919303428</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.524090615322951</v>
+        <v>-2.518027306571487</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.664059181483945</v>
+        <v>1.667697166734823</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.08922262854266</v>
+        <v>-9.948378511750551</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8674154063660064</v>
+        <v>-0.811077759649161</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.524090615322951</v>
+        <v>-2.518027306571487</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.654175700171037</v>
+        <v>1.657813685421915</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.821980827674267</v>
+        <v>-9.681136710882154</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7623532465180207</v>
+        <v>-0.7060155998011752</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.524090615322951</v>
+        <v>-2.518027306571487</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.652341139671663</v>
+        <v>1.655979124922542</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.724073788997776</v>
+        <v>-9.583229672205663</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7234907460208855</v>
+        <v>-0.66715309930404</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.456104865462394</v>
+        <v>-2.45004155671093</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.692832274614536</v>
+        <v>1.696470259865415</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.700120248021818</v>
+        <v>-9.559276131229705</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7132408234850085</v>
+        <v>-0.656903176768163</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.432151324486437</v>
+        <v>-2.426088015734973</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.707872905345605</v>
+        <v>1.711510890596483</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.436060309699021</v>
+        <v>-9.295216192906908</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6208771643176418</v>
+        <v>-0.5645395176007968</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.168091386163641</v>
+        <v>-2.162028077412177</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.85304855217753</v>
+        <v>1.856686537428408</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.728980686194184</v>
+        <v>-8.588136569402071</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3408323485760079</v>
+        <v>-0.2844947018591624</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.168091386163641</v>
+        <v>-2.162028077412177</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.850261518517229</v>
+        <v>1.853899503768107</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.688796387827994</v>
+        <v>-8.54795227103588</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3244150053416903</v>
+        <v>-0.2680773586248448</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.12790708779745</v>
+        <v>-2.121843779045986</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.874715721424785</v>
+        <v>1.878353706675663</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.52539651688863</v>
+        <v>-8.384552400096517</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.259688235745188</v>
+        <v>-0.2033505890283429</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.964507216858087</v>
+        <v>-1.958443908106624</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.972122465209159</v>
+        <v>1.975760450460037</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.291915294659031</v>
+        <v>-8.151071177866918</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.158371318015496</v>
+        <v>-0.1020336712986505</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.731025994628489</v>
+        <v>-1.724962685877025</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.120135627384771</v>
+        <v>2.123773612635649</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.801637122785787</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.142248903651517</v>
+        <v>-8.001404786859403</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1013969719254493</v>
+        <v>-0.04505932520860378</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.638122503385953</v>
+        <v>-1.632059194634489</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.172985511817333</v>
+        <v>2.176623497068212</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390428</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.009973430020629</v>
+        <v>-7.869129313228517</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.05311929572606733</v>
+        <v>0.003218350990777719</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.505847029755066</v>
+        <v>-1.499783721003602</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.247718282742892</v>
+        <v>2.251356267993771</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.819373755347477</v>
+        <v>-7.678529638555364</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.02593563483083017</v>
+        <v>0.08227328154767566</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.315247355081913</v>
+        <v>-1.30918404633045</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.364893148234421</v>
+        <v>2.368531133485299</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960987</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.570373956663896</v>
+        <v>-7.429529839871783</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1384418955279214</v>
+        <v>0.1947795422447669</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.315247355081913</v>
+        <v>-1.30918404633045</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.377799489458079</v>
+        <v>2.381437474708958</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607646</v>
+        <v>3.692931855607645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.675963946437</v>
+        <v>-7.535119829644888</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.03177002998053879</v>
+        <v>0.02456761673630625</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.420837344855018</v>
+        <v>-1.414774036103554</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.186469565994998</v>
+        <v>2.190107551245876</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.694698848555597</v>
+        <v>-7.553854731763485</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.009280351049108404</v>
+        <v>0.06561799776595389</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.426433354515149</v>
+        <v>-1.420370045763685</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.231656302076006</v>
+        <v>2.235294287326884</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710812</v>
+        <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.546758807147998</v>
+        <v>-7.405914690355885</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.05142255507601945</v>
+        <v>0.004915091640826041</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.406112438606591</v>
+        <v>-1.400049129855128</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.123969928932973</v>
+        <v>2.127607914183851</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.493789284894009</v>
+        <v>-7.352945168101897</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.03894873242790187</v>
+        <v>0.01738891428894318</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.353142916352602</v>
+        <v>-1.347079607601139</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.147037656031888</v>
+        <v>2.150675641282766</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098109</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.450240878123319</v>
+        <v>-7.309396761331207</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.02848998181471885</v>
+        <v>0.0278476649021262</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.353142916352602</v>
+        <v>-1.347079607601139</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.140077043936795</v>
+        <v>2.143715029187673</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78292253349342</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.208092484669461</v>
+        <v>-7.067248367877348</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.0828317299479675</v>
+        <v>0.1391693766648125</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.353142916352602</v>
+        <v>-1.347079607601139</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.154539398317938</v>
+        <v>2.158177383568816</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722817</v>
+        <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.099833347546939</v>
+        <v>-6.958989230754827</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1206675052561712</v>
+        <v>0.1770051519730163</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.353142916352602</v>
+        <v>-1.347079607601139</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.149071518777133</v>
+        <v>2.152709504028011</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.976542212729808</v>
+        <v>-6.835698095937696</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1674820531936003</v>
+        <v>0.2238196999104454</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.229851781535472</v>
+        <v>-1.223788472784008</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.220544293677988</v>
+        <v>2.224182278928866</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.955393013826365</v>
+        <v>-6.814548897034252</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1836427109923027</v>
+        <v>0.2399803577091482</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.208702582632029</v>
+        <v>-1.202639273880565</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.240934791257379</v>
+        <v>2.244572776508257</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318093</v>
+        <v>3.748328408318092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.711627571842921</v>
+        <v>-6.570783455050808</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2769295961327312</v>
+        <v>0.3332672428495767</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.208702582632029</v>
+        <v>-1.202639273880565</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.23671549960443</v>
+        <v>2.240353484855308</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057526</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.609864751565626</v>
+        <v>-6.469020634773513</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.319759038163665</v>
+        <v>0.3760966848805105</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.1954835142396</v>
+        <v>-1.189420205488136</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.246771254559903</v>
+        <v>2.250409239810781</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.360014357616551</v>
+        <v>-6.219170240824439</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4124412707269971</v>
+        <v>0.4687789174438426</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.1954835142396</v>
+        <v>-1.189420205488136</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.239513329543605</v>
+        <v>2.243151314794483</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011499</v>
+        <v>3.835957987011498</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.184122265149119</v>
+        <v>-6.043278148357007</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4863972312346188</v>
+        <v>0.5427348779514638</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.1954835142396</v>
+        <v>-1.189420205488136</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.243112453064254</v>
+        <v>2.246750438315132</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.012675802126656</v>
+        <v>-5.871831685334543</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5683033224981577</v>
+        <v>0.6246409692150032</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.024037051217137</v>
+        <v>-1.017973742465673</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.359307836932286</v>
+        <v>2.362945822183164</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.938386236388316</v>
+        <v>-5.797542119596204</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5970396264097904</v>
+        <v>0.6533772731266358</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9497474854787973</v>
+        <v>-0.9436841767273336</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.402902053991586</v>
+        <v>2.406540039242465</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.874750494154382</v>
+        <v>-5.73390637736227</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6271887243576817</v>
+        <v>0.6835263710745267</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8861117432448627</v>
+        <v>-0.8800484344933991</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.445778300386264</v>
+        <v>2.449416285637143</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.763323734828462</v>
+        <v>-5.622479618036349</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6529536868718453</v>
+        <v>0.7092913335886903</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8861117432448627</v>
+        <v>-0.8800484344933991</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.42697255917006</v>
+        <v>2.430610544420938</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.522893238023602</v>
+        <v>-5.382049121231489</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7508689622186666</v>
+        <v>0.8072066089355121</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6456812464400025</v>
+        <v>-0.6396179376885388</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.572973933877853</v>
+        <v>2.576611919128732</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.450650669852407</v>
+        <v>-5.309806553060294</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7836953033219647</v>
+        <v>0.8400329500388102</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6456812464400025</v>
+        <v>-0.6396179376885388</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.576903247712674</v>
+        <v>2.580541232963552</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.397652347571019</v>
+        <v>-5.256808230778907</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8055732161518598</v>
+        <v>0.8619108628687053</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5903449874380636</v>
+        <v>-0.5842816786866</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.610783587031177</v>
+        <v>2.614421572282055</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.288847462091292</v>
+        <v>-5.14800334529918</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8460932415637443</v>
+        <v>0.9024308882805894</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5903449874380636</v>
+        <v>-0.5842816786866</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.607781658251171</v>
+        <v>2.611419643502049</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.068826664054281</v>
+        <v>-4.927982547262169</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9356805977891627</v>
+        <v>0.992018244506008</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4491251423700834</v>
+        <v>-0.4430618336186197</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.694092602302573</v>
+        <v>2.697730587553451</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.935958974991004</v>
+        <v>-4.795114858198891</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.004721856216297</v>
+        <v>1.061059502933142</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4491251423700834</v>
+        <v>-0.4430618336186197</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.709986785104396</v>
+        <v>2.713624770355274</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496261</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.815785891626505</v>
+        <v>-4.674941774834393</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.053936934002398</v>
+        <v>1.110274580719244</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.3289520590055844</v>
+        <v>-0.3228887502541208</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.783236479563397</v>
+        <v>2.786874464814276</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.671113746526768</v>
+        <v>-4.530269629734655</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.121893894603733</v>
+        <v>1.178231541320578</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.184279913905847</v>
+        <v>-0.1782166051543834</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.88012786918468</v>
+        <v>2.883765854435558</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942103</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.73098857388446</v>
+        <v>-4.590144457092348</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.083981455062082</v>
+        <v>1.140319101778927</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2441547412635391</v>
+        <v>-0.2380914325120755</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.83024046417149</v>
+        <v>2.833878449422368</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674515</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.644189076105452</v>
+        <v>-4.503344959313339</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.141101747496251</v>
+        <v>1.197439394213097</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2441547412635391</v>
+        <v>-0.2380914325120755</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.852640957494056</v>
+        <v>2.856278942744934</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430695</v>
+        <v>3.729146398430694</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.646658782567258</v>
+        <v>-4.505814665775145</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.140186266284941</v>
+        <v>1.196523913001787</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.2466244477253453</v>
+        <v>-0.2405611389738816</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.851231534990385</v>
+        <v>2.854869520241263</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.715028968891268</v>
+        <v>-4.574184852099155</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.123845114230039</v>
+        <v>1.180182760946884</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.2373487486891304</v>
+        <v>-0.2312854399376667</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.867803876886815</v>
+        <v>2.871441862137694</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.823567149807402</v>
+        <v>-4.682723033015289</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.070866550495477</v>
+        <v>1.127204197212322</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.2373487486891304</v>
+        <v>-0.2312854399376667</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.858240585518707</v>
+        <v>2.861878570769585</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.854560309136107</v>
+        <v>-4.713716192343995</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8831788518043815</v>
+        <v>0.9395164985212268</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.2373487486891304</v>
+        <v>-0.2312854399376667</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.682950150559094</v>
+        <v>2.686588135809972</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.679086049343638</v>
+        <v>-4.538241932551526</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9579357877131569</v>
+        <v>1.014273434430002</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.2373487486891304</v>
+        <v>-0.2312854399376667</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.687517382550881</v>
+        <v>2.69115536780176</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.790022301984887</v>
+        <v>-4.649178185192775</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8893033154178642</v>
+        <v>0.9456409621347097</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.2373487486891304</v>
+        <v>-0.2312854399376667</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.663259411312088</v>
+        <v>2.666897396562967</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.756358756512605</v>
+        <v>-4.615514639720493</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9059001188266826</v>
+        <v>0.9622377655435281</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2036852032168485</v>
+        <v>-0.1976218944653849</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.686588923815363</v>
+        <v>2.690226909066241</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.696506137308882</v>
+        <v>-4.555662020516769</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9400135529403044</v>
+        <v>0.9963511996571497</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2036852032168485</v>
+        <v>-0.1976218944653849</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.696761310247496</v>
+        <v>2.700399295498374</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.610262674282504</v>
+        <v>-4.469418557490392</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9694572087247157</v>
+        <v>1.025794855441561</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2036852032168485</v>
+        <v>-0.1976218944653849</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.691707580821356</v>
+        <v>2.695345566072234</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.655569493681484</v>
+        <v>-4.514725376889372</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9431102564096494</v>
+        <v>0.9994479031264947</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2444953662260793</v>
+        <v>-0.2384320574746157</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.658997258460343</v>
+        <v>2.662635243711221</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.684602598383785</v>
+        <v>-4.543758481591673</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9320488875618305</v>
+        <v>0.9883865342786757</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2444953662260793</v>
+        <v>-0.2384320574746157</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.659549131493445</v>
+        <v>2.663187116744323</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.591792116932925</v>
+        <v>-4.450948000140813</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8984457720335399</v>
+        <v>0.9547834187503854</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.15168488477522</v>
+        <v>-0.1456215760237563</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.644508112255326</v>
+        <v>2.648146097506204</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.636181586262353</v>
+        <v>-4.495337469470241</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8825634602263699</v>
+        <v>0.9389011069432152</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1960743541046476</v>
+        <v>-0.190011045353184</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.61974790658227</v>
+        <v>2.623385891833148</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.523510368026103</v>
+        <v>-4.38266625123399</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9227076560325929</v>
+        <v>0.9790453027494381</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.08340313586839743</v>
+        <v>-0.07733982711693377</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.682426346035743</v>
+        <v>2.686064331286621</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.41113336684343</v>
+        <v>-4.270289250051317</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9731497523363293</v>
+        <v>1.029487399053175</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.08340313586839743</v>
+        <v>-0.07733982711693377</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.68791764186641</v>
+        <v>2.691555627117288</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.438913764744782</v>
+        <v>-4.29806964795267</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9735347949443274</v>
+        <v>1.029872441661173</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1111835337697505</v>
+        <v>-0.1051202250182868</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.682746604894138</v>
+        <v>2.686384590145016</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.521915045770061</v>
+        <v>-4.381070928977949</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7786900025348691</v>
+        <v>0.8350276492517144</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1297544182969242</v>
+        <v>-0.1236911095454606</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.509959794178487</v>
+        <v>2.513597779429365</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.630529124213393</v>
+        <v>-4.48968500742128</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8553940318767421</v>
+        <v>0.9117316785935876</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1297544182969242</v>
+        <v>-0.1236911095454606</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.630109454897692</v>
+        <v>2.633747440148571</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.717127707194495</v>
+        <v>-4.576283590402383</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.835267624786624</v>
+        <v>0.8916052715034692</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1297544182969242</v>
+        <v>-0.1236911095454606</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.644622481000015</v>
+        <v>2.648260466250894</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.678744044636344</v>
+        <v>-4.537899927844232</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8480405311522532</v>
+        <v>0.9043781778690985</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.09137075573877307</v>
+        <v>-0.08530744698730941</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.665072119877275</v>
+        <v>2.668710105128153</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.501627714601178</v>
+        <v>-4.360783597809066</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9156160920116214</v>
+        <v>0.9719537387284669</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.09137075573877307</v>
+        <v>-0.08530744698730941</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.661801148722577</v>
+        <v>2.665439133973455</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.546719959434724</v>
+        <v>-4.405875842642612</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8982625858401163</v>
+        <v>0.9546002325569616</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1532667989081629</v>
+        <v>-0.1472034901566992</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.625346914582856</v>
+        <v>2.628984899833734</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.367344538195956</v>
+        <v>-4.226500421403844</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9637997296420378</v>
+        <v>1.020137376358883</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.003509959262555817</v>
+        <v>0.009573268014019476</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.713199944791701</v>
+        <v>2.716837930042579</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.412358751716562</v>
+        <v>-4.27151463492445</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9266014995653853</v>
+        <v>0.9829391462822306</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.02683893605204879</v>
+        <v>-0.02077562730058513</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.675798062934528</v>
+        <v>2.679436048185407</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.679363261988997</v>
+        <v>-4.538519145196885</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.825491257795357</v>
+        <v>0.8818289045122023</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2212019740949974</v>
+        <v>-0.2151386653435337</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.564871802447705</v>
+        <v>2.568509787698583</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.78056104342617</v>
+        <v>-4.639716926634057</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7842160671169893</v>
+        <v>0.8405537138338346</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2896107876403166</v>
+        <v>-0.2835474788888529</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.523030436217015</v>
+        <v>2.526668421467893</v>
       </c>
     </row>
     <row r="1961">
@@ -46651,19 +46651,19 @@
         <v>3.705571661815456</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.753410111293847</v>
+        <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.788624329075721</v>
+        <v>-4.607241340463285</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8376039553498111</v>
+        <v>0.8511439098564602</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2896107876403166</v>
+        <v>-0.2835474788888529</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.579643638709657</v>
+        <v>2.52426838302221</v>
       </c>
     </row>
     <row r="1962">
@@ -46674,19 +46674,19 @@
         <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.749934830502092</v>
+        <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.769586201368424</v>
+        <v>-4.588203212755988</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8417439256409749</v>
+        <v>0.8552838801476241</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3477943989715111</v>
+        <v>-0.3417310902200474</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.541258191119185</v>
+        <v>2.485882935431738</v>
       </c>
     </row>
     <row r="1963">
@@ -46697,19 +46697,19 @@
         <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.927516699440772</v>
+        <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.800712832519042</v>
+        <v>-4.619329843906606</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.006875142119408</v>
+        <v>1.020415096626057</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3477943989715111</v>
+        <v>-0.3417310902200474</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.718840060057866</v>
+        <v>2.663464804370419</v>
       </c>
     </row>
     <row r="1964">
@@ -46720,19 +46720,19 @@
         <v>3.722447362067867</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.928350028426906</v>
+        <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.81457959385296</v>
+        <v>-4.633196605240524</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.002161766571974</v>
+        <v>1.015701721078624</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.385652315705334</v>
+        <v>-0.3795890069538704</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.696958639003705</v>
+        <v>2.641583383316258</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.787425580789124</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.934358558823832</v>
+        <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.834836892381918</v>
+        <v>-4.653453903769482</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.000067377557317</v>
+        <v>1.013607332063966</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.385652315705334</v>
+        <v>-0.3795890069538704</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.702967169400631</v>
+        <v>2.647591913713184</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.781501250519911</v>
       </c>
       <c r="C1966" t="n">
-        <v>3.013511206615854</v>
+        <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.687093922146915</v>
+        <v>-4.50571093353448</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.13831721344334</v>
+        <v>1.151857167949989</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2178449584704509</v>
+        <v>-0.2117816497189872</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.882804231533584</v>
+        <v>2.827428975846136</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.802245929181173</v>
       </c>
       <c r="C1967" t="n">
-        <v>3.016304828147335</v>
+        <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.789108604678137</v>
+        <v>-4.607725616065701</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.100304961962333</v>
+        <v>1.113844916468982</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2178449584704509</v>
+        <v>-0.2117816497189872</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.885597853065065</v>
+        <v>2.830222597377617</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394734</v>
       </c>
       <c r="C1968" t="n">
-        <v>3.016967176538993</v>
+        <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.782955898625352</v>
+        <v>-4.601572910012917</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.103428392775105</v>
+        <v>1.116968347281754</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2116922524176666</v>
+        <v>-0.2056289436662029</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.889951825088393</v>
+        <v>2.834576569400946</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
-        <v>3.016047653279103</v>
+        <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.799765196775854</v>
+        <v>-4.618382208163418</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.095785150255014</v>
+        <v>1.109325104761663</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.2285015505681682</v>
+        <v>-0.2224382418167046</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.878946722938203</v>
+        <v>2.823571467250755</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.082383207075924</v>
+        <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.737467197999732</v>
+        <v>-4.556084209387296</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.187039903562284</v>
+        <v>1.200579858068933</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.2285015505681682</v>
+        <v>-0.2224382418167046</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.945282276735024</v>
+        <v>2.889907021047576</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992194</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.790964079465322</v>
+        <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.535677000334574</v>
+        <v>-4.354294011722138</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9763368550177454</v>
+        <v>0.9898768095243944</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.03048335839901384</v>
+        <v>-0.02442004964755018</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.772674064425914</v>
+        <v>2.717298808738467</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.861254311787497</v>
+        <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.475786318691981</v>
+        <v>-4.294403330079545</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.070583359996958</v>
+        <v>1.084123314503607</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.02940732324357964</v>
+        <v>0.0354706319950433</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.878898705733645</v>
+        <v>2.823523450046198</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319549</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.875882047903541</v>
+        <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.573526863316955</v>
+        <v>-4.392143874704519</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.046114878263012</v>
+        <v>1.059654832769661</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.01351804511059945</v>
+        <v>0.01958135386206311</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.883992874969901</v>
+        <v>2.828617619282454</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489388</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.874418028728213</v>
+        <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.749864623439884</v>
+        <v>-4.568481634827449</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9741157550385116</v>
+        <v>0.9876557095451608</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.1628197150123299</v>
+        <v>-0.1567564062608663</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.776726199720815</v>
+        <v>2.721350944033368</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397798</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.872909646768141</v>
+        <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.673442577007958</v>
+        <v>-4.492059588395522</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.003176191651211</v>
+        <v>1.01671614615786</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.1628197150123299</v>
+        <v>-0.1567564062608663</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.775217817760744</v>
+        <v>2.719842562073296</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316253</v>
+        <v>3.836023391024966</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.872772514203577</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.629069445369389</v>
+        <v>-4.447686456756953</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.020788311742075</v>
+        <v>1.034328266248724</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.1184465833737613</v>
+        <v>-0.1123832746222977</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.801704564179321</v>
+        <v>2.746329308491874</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821591150863226</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.867166308342168</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.540915233630213</v>
+        <v>-4.439732486462181</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.050443790576336</v>
+        <v>1.037509854366633</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.1184465833737613</v>
+        <v>-0.1123832746222977</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.796098358317912</v>
+        <v>2.746329308491874</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190325</v>
+        <v>3.833040181947585</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.873548065369972</v>
+        <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.493259503069157</v>
+        <v>-4.392076755901125</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.075887839828562</v>
+        <v>1.06295390361886</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.0707908528127057</v>
+        <v>-0.06472754406124204</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.831073553682349</v>
+        <v>2.781304503856312</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.822707244326877</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.878440438744697</v>
+        <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.365575193274861</v>
+        <v>-4.264392446106829</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.131853937121005</v>
+        <v>1.118920000911303</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.05689345698159076</v>
+        <v>0.06295676573305442</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.912576512933652</v>
+        <v>2.862807463107614</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557293</v>
+        <v>3.828837911314553</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.865195111220569</v>
+        <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.42624178367725</v>
+        <v>-4.325059036509217</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.094341973435922</v>
+        <v>1.08140803722622</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.02480485973694291</v>
+        <v>-0.01874155098547925</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.850312195378404</v>
+        <v>2.800543145552366</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932769</v>
+        <v>3.816866067690029</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.869292813831198</v>
+        <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.381403382068852</v>
+        <v>-4.280220634900819</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.11637503668991</v>
+        <v>1.103441100480208</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.02026142679207343</v>
+        <v>-0.01419811804060978</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.857135957755954</v>
+        <v>2.807366907929917</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917053</v>
+        <v>3.817961388674313</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.873453753462276</v>
+        <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.48216201782585</v>
+        <v>-4.380979270657817</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.080232522018189</v>
+        <v>1.067298585808486</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.1090869955190789</v>
+        <v>-0.1030236867676152</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.808001556150828</v>
+        <v>2.758232506324791</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405962</v>
+        <v>3.826713779163222</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.879333355990113</v>
+        <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.437959180739949</v>
+        <v>-4.336776433571917</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.103793259380386</v>
+        <v>1.090859323170684</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.06488415843317841</v>
+        <v>-0.05882084968171475</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.840402860930206</v>
+        <v>2.790633811104169</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265647</v>
+        <v>3.838228663022907</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.87774335645936</v>
+        <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.474938208403392</v>
+        <v>-4.373755461235359</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.087411648784256</v>
+        <v>1.074477712574554</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.02791025664184787</v>
+        <v>-0.02184694789038422</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.860997202474252</v>
+        <v>2.811228152648215</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284881</v>
+        <v>3.863924114042141</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.9289911216424</v>
+        <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.494996287268233</v>
+        <v>-4.3938135401002</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.13063618242136</v>
+        <v>1.117702246211658</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.02791025664184787</v>
+        <v>-0.02184694789038422</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.912244967657291</v>
+        <v>2.862475917831254</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321024</v>
+        <v>3.865367715078284</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.927431826236653</v>
+        <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.455065614090342</v>
+        <v>-4.35388286692231</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.145049156286769</v>
+        <v>1.132115220077067</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.01202041653604247</v>
+        <v>0.01808372528750612</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.934644076158279</v>
+        <v>2.884875026332241</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475141</v>
+        <v>3.864518876232401</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.922380054474923</v>
+        <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.404033521367815</v>
+        <v>-4.302850774199782</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.16041022161405</v>
+        <v>1.147476285404348</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.06305250925857042</v>
+        <v>0.06911581801003408</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.960211560030066</v>
+        <v>2.910442510204029</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404857</v>
+        <v>3.842576394162116</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.939567458567628</v>
+        <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.338809340240609</v>
+        <v>-4.237626593072576</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.203687298157637</v>
+        <v>1.190753361947935</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.128276690385776</v>
+        <v>0.1343399991372397</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.016533472799094</v>
+        <v>2.966764422973057</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.84006118688256</v>
+        <v>3.84009022063982</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.935528430866909</v>
+        <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.301382320169475</v>
+        <v>-4.200199573001442</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.214619078485371</v>
+        <v>1.201685142275669</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.1335282284149577</v>
+        <v>0.1395915371664214</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.015645367915883</v>
+        <v>2.965876318089846</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992665</v>
+        <v>3.845198842749925</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.936785223198149</v>
+        <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.321493976204184</v>
+        <v>-4.220311229036151</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.207831208402728</v>
+        <v>1.194897272193026</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.1445555734123769</v>
+        <v>0.1506188821638406</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.023518567245575</v>
+        <v>2.973749517419538</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636292</v>
+        <v>3.828690479393551</v>
       </c>
       <c r="C1991" t="n">
-        <v>3.09734299421936</v>
+        <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.267749161776979</v>
+        <v>-4.166566414608946</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.389886905194821</v>
+        <v>1.376952968985119</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.1546188828528389</v>
+        <v>0.1606821916043025</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.190114323931063</v>
+        <v>3.140345274105026</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.81322282095763</v>
+        <v>3.813251854714889</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.217455903437177</v>
+        <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.243957593170837</v>
+        <v>-4.142774846002804</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.519516441855095</v>
+        <v>1.506582505645393</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.1784104514589812</v>
+        <v>0.1844737602104448</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.324502174312566</v>
+        <v>3.274733124486529</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998755</v>
+        <v>3.814259761756015</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.209163879451036</v>
+        <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.217873508907029</v>
+        <v>-4.116690761738996</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.521658051574477</v>
+        <v>1.508724115364775</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.1784104514589812</v>
+        <v>0.1844737602104448</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.316210150326425</v>
+        <v>3.266441100500387</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896929</v>
+        <v>3.803426852654189</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.207357075034815</v>
+        <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.213539205849981</v>
+        <v>-4.015845863498491</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.521584968381076</v>
+        <v>1.547255270244756</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.3300605547781851</v>
+        <v>0.3969725277772699</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.405393407901727</v>
+        <v>3.392133556624262</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.79626414395986</v>
+        <v>3.79629317771712</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.224911480761607</v>
+        <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.204646744456698</v>
+        <v>-4.006953402105208</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.54269635866518</v>
+        <v>1.568366660528861</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.3300605547781851</v>
+        <v>0.3969725277772699</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.422947813628518</v>
+        <v>3.409687962351053</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945368</v>
+        <v>3.794453975702628</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.216766528166191</v>
+        <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.373122861426575</v>
+        <v>-4.175429519075085</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.467160959281813</v>
+        <v>1.492831261145494</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.3021127190616043</v>
+        <v>0.3690246920606891</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.398034159603153</v>
+        <v>3.384774308325689</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782711</v>
+        <v>3.795603100539971</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.287179189623034</v>
+        <v>3.233772154546119</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.675323332564992</v>
+        <v>-3.477629990213502</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.81669343228329</v>
+        <v>1.842363734146971</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.2317646596911936</v>
+        <v>0.2986766326902784</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.42623798543775</v>
+        <v>3.412978134160286</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632641</v>
+        <v>3.784700379389901</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.277843212119939</v>
+        <v>3.224436177043023</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.652602228881839</v>
+        <v>-3.45490888653035</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.816445896253456</v>
+        <v>1.842116198117136</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.2317646596911936</v>
+        <v>0.2986766326902784</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.416902007934655</v>
+        <v>3.40364215665719</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777679</v>
+        <v>3.783234730534939</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.436749337971108</v>
+        <v>3.383342302894192</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.792894828419032</v>
+        <v>-3.595201486067542</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.919234982289748</v>
+        <v>1.944905284153428</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.09147206015400094</v>
+        <v>0.1583840331530857</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.491632574063509</v>
+        <v>3.478372722786044</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644417</v>
+        <v>3.779962759401677</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.473827160464754</v>
+        <v>3.420420125387839</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.947675835197287</v>
+        <v>-3.749982492845797</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.894400402072092</v>
+        <v>1.920070703935773</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.05810438609952484</v>
+        <v>0.1250163590986096</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.50868979212447</v>
+        <v>3.495429940847005</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.773644570866075</v>
+        <v>3.769472653557226</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.4705025164543</v>
+        <v>3.417095481377384</v>
       </c>
       <c r="D2001" t="n">
-        <v>-4.014936279219204</v>
+        <v>-3.817242936867714</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.864171580452871</v>
+        <v>1.889841882316551</v>
       </c>
       <c r="F2001" t="n">
-        <v>-0.009156057922392269</v>
+        <v>0.05775591507669253</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.465008881700864</v>
+        <v>3.4517490304234</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.570844818288085</v>
+        <v>3.849137925783207</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.34319605937123</v>
+        <v>3.507800395636292</v>
       </c>
       <c r="D2002" t="n">
-        <v>-4.014936279219204</v>
+        <v>-3.817242936867714</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.864171580452871</v>
+        <v>1.889841882316551</v>
       </c>
       <c r="F2002" t="n">
-        <v>-0.009156057922392269</v>
+        <v>0.05775591507669253</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.336259856357597</v>
+        <v>3.50086419262266</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240621.xlsx
+++ b/tame_output/ON/bt/strategyON_20240621.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.2%</t>
+          <t>49.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>17.0%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,37 +844,37 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>15.0%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.2%</t>
+          <t>-75.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.9%</t>
+          <t>108.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.0%</t>
+          <t>123.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.3%</t>
+          <t>93.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-683.2%</t>
+          <t>-665.2%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.0%</t>
+          <t>-49.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-69.6%</t>
+          <t>-71.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>90.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>455.4%</t>
+          <t>429.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-10.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-543.3%</t>
+          <t>-577.3%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-273.7%</t>
+          <t>-266.5%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,32 +1150,32 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-39.8%</t>
+          <t>-40.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-29.5%</t>
+          <t>-35.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-187.2%</t>
+          <t>-215.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-22.2%</t>
+          <t>-24.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,27 +1293,27 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-291.7%</t>
+          <t>-273.7%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.6%</t>
+          <t>-30.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-15.2%</t>
+          <t>-17.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>-29.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-194.4%</t>
+          <t>-171.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-218.2%</t>
+          <t>-235.2%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>95.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-175.4%</t>
+          <t>-164.6%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.1%</t>
+          <t>-27.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-95.9%</t>
+          <t>-126.1%</t>
         </is>
       </c>
     </row>
@@ -43733,16 +43733,16 @@
         <v>3.13991794227561</v>
       </c>
       <c r="D1834" t="n">
-        <v>0.7497961784502833</v>
+        <v>0.9296086660691371</v>
       </c>
       <c r="E1834" t="n">
-        <v>3.439479989341976</v>
+        <v>3.511404984389518</v>
       </c>
       <c r="F1834" t="n">
-        <v>1.631764624679707</v>
+        <v>1.811577112298561</v>
       </c>
       <c r="G1834" t="n">
-        <v>4.118976717083434</v>
+        <v>4.226864209654747</v>
       </c>
     </row>
     <row r="1835">
@@ -43756,16 +43756,16 @@
         <v>3.138175778137954</v>
       </c>
       <c r="D1835" t="n">
-        <v>0.5532457673970779</v>
+        <v>0.7330582550159315</v>
       </c>
       <c r="E1835" t="n">
-        <v>3.359117660783038</v>
+        <v>3.43104265583058</v>
       </c>
       <c r="F1835" t="n">
-        <v>1.668418790368211</v>
+        <v>1.848231277987064</v>
       </c>
       <c r="G1835" t="n">
-        <v>4.139227052358882</v>
+        <v>4.247114544930193</v>
       </c>
     </row>
     <row r="1836">
@@ -43779,16 +43779,16 @@
         <v>3.118001050765402</v>
       </c>
       <c r="D1836" t="n">
-        <v>0.3997263829116132</v>
+        <v>0.5795388705304668</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.2775351796163</v>
+        <v>3.349460174663841</v>
       </c>
       <c r="F1836" t="n">
-        <v>1.705385264837735</v>
+        <v>1.885197752456588</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.141232209668043</v>
+        <v>4.249119702239355</v>
       </c>
     </row>
     <row r="1837">
@@ -43802,16 +43802,16 @@
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.2177198195886446</v>
+        <v>0.3975323072074982</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.205221693012986</v>
+        <v>3.277146688060528</v>
       </c>
       <c r="F1837" t="n">
-        <v>1.705385264837735</v>
+        <v>1.885197752456588</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.141721348393917</v>
+        <v>4.249608840965229</v>
       </c>
     </row>
     <row r="1838">
@@ -43825,16 +43825,16 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.1694975527415611</v>
+        <v>0.3493100403604147</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.19001276889582</v>
+        <v>3.261937763943361</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.657162997990651</v>
+        <v>1.836975485609505</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.116867970907334</v>
+        <v>4.224755463478646</v>
       </c>
     </row>
     <row r="1839">
@@ -43848,16 +43848,16 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>-0.06763393910823401</v>
+        <v>0.1121785485106196</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.130101256653444</v>
+        <v>3.202026251700985</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.657162997990651</v>
+        <v>1.836975485609505</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.151809055404875</v>
+        <v>4.259696547976187</v>
       </c>
     </row>
     <row r="1840">
@@ -43871,16 +43871,16 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>-0.06259634838064748</v>
+        <v>0.1172161392382061</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.130693733129816</v>
+        <v>3.202618728177358</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.712807454256969</v>
+        <v>1.892619941875822</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.183773169350004</v>
+        <v>4.291660661921316</v>
       </c>
     </row>
     <row r="1841">
@@ -43894,16 +43894,16 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.3197903830887042</v>
+        <v>-0.1399778954698506</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.006562500870331</v>
+        <v>3.078487495917872</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.455613419548912</v>
+        <v>1.635425907167765</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.008203130148907</v>
+        <v>4.116090622720219</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.3855577731381163</v>
+        <v>-0.2057452855192627</v>
       </c>
       <c r="E1842" t="n">
-        <v>2.981273153981036</v>
+        <v>3.053198149028577</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.455613419548912</v>
+        <v>1.635425907167765</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.009220739279377</v>
+        <v>4.117108231850689</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.5908024501953608</v>
+        <v>-0.4109899625765073</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.889803315145894</v>
+        <v>2.961728310193435</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.455613419548912</v>
+        <v>1.635425907167765</v>
       </c>
       <c r="G1843" t="n">
-        <v>3.999848771267133</v>
+        <v>4.107736263838444</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.6725743506231125</v>
+        <v>-0.4927618630042589</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.847177280930031</v>
+        <v>2.919102275977573</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.482648992955049</v>
+        <v>1.662461480573902</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.006152841266053</v>
+        <v>4.114040333837365</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.7397834584949903</v>
+        <v>-0.5599709708761367</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.825058954614982</v>
+        <v>2.896983949662524</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.482648992955049</v>
+        <v>1.662461480573902</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.010918158099756</v>
+        <v>4.118805650671067</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.9473492428866022</v>
+        <v>-0.7675367552677486</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.739857436977578</v>
+        <v>2.81178243202512</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.275083208563437</v>
+        <v>1.45489569618229</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.884203483584028</v>
+        <v>3.992090976155341</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.365103266433439</v>
+        <v>-1.185290778814586</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.570682719063906</v>
+        <v>2.642607714111448</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.8573291850165997</v>
+        <v>1.037141672635453</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.631477960960989</v>
+        <v>3.739365453532302</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.65523493303887</v>
+        <v>-1.475422445420017</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.454496269020656</v>
+        <v>2.526421264068197</v>
       </c>
       <c r="F1848" t="n">
-        <v>0.8814109797567796</v>
+        <v>1.061223467375633</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.645793254404019</v>
+        <v>3.753680746975331</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.863238991391948</v>
+        <v>-1.683426503773094</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.37618679023335</v>
+        <v>2.448111785280891</v>
       </c>
       <c r="F1849" t="n">
-        <v>0.8814109797567796</v>
+        <v>1.061223467375633</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.650685398957944</v>
+        <v>3.758572891529257</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-2.074651412279923</v>
+        <v>-1.89483892466107</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.286703278216148</v>
+        <v>2.358628273263689</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.6699985588688046</v>
+        <v>0.849811046487658</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.518919402763148</v>
+        <v>3.62680689533446</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.440720139424576</v>
+        <v>-2.260907651805722</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.133360086664736</v>
+        <v>2.205285081712277</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.3039298317241519</v>
+        <v>0.4837423193430054</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.292362465782805</v>
+        <v>3.400249958354117</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.649210920876261</v>
+        <v>-2.469398433257406</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.07030206382283</v>
+        <v>2.142227058870372</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.09543905027246746</v>
+        <v>0.275251537891321</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.187606286650563</v>
+        <v>3.295493779221875</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.896412105641482</v>
+        <v>-2.716599618022628</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.97952034032531</v>
+        <v>2.051445335372852</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.1155924037712799</v>
+        <v>0.2954048913901334</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.207797049158418</v>
+        <v>3.315684541729731</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.388797133665579</v>
+        <v>-3.208984646046725</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.783672721159404</v>
+        <v>1.855597716206945</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.3767926242528168</v>
+        <v>-0.1969801366339634</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.913472424387693</v>
+        <v>3.021359916959005</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.773977524595651</v>
+        <v>-3.594165036976797</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.628143103600238</v>
+        <v>1.70006809864778</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.3767926242528168</v>
+        <v>-0.1969801366339634</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.912014963200556</v>
+        <v>3.019902455771868</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.023848204610233</v>
+        <v>-3.844035716991379</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.529963955049022</v>
+        <v>1.601888950096563</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.3405299044223536</v>
+        <v>-0.1607174168035001</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.93554171855345</v>
+        <v>3.043429211124762</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.230359981497254</v>
+        <v>-4.050547493878399</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.443465302950471</v>
+        <v>1.515390297998013</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.547041681309375</v>
+        <v>-0.3672291936905216</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.807740711077495</v>
+        <v>2.915628203648807</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.549704056577756</v>
+        <v>-4.369891568958901</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.31750059961853</v>
+        <v>1.389425594666071</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.547041681309375</v>
+        <v>-0.3672291936905216</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.809513637777755</v>
+        <v>2.917401130349067</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.981509849727543</v>
+        <v>-4.801697362108689</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.131111169826019</v>
+        <v>1.203036164873561</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.683459177750642</v>
+        <v>-0.5036466901317886</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.713996027380399</v>
+        <v>2.821883519951711</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.216203843860096</v>
+        <v>-5.036391356241241</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.025518347175089</v>
+        <v>1.09744334222263</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.6771229105213868</v>
+        <v>-0.4973104229025335</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.706082562720043</v>
+        <v>2.813970055291355</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.551866491090548</v>
+        <v>-5.372054003471693</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8898338799388732</v>
+        <v>0.9617588749864145</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.7450538960102917</v>
+        <v>-0.5652414083914383</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.663904563082665</v>
+        <v>2.771792055653977</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.915492735990862</v>
+        <v>-5.735680248372007</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7508709422129893</v>
+        <v>0.8227959372605307</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.8432755328774175</v>
+        <v>-0.6634630452585641</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.611459141196631</v>
+        <v>2.719346633767943</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.280620118629608</v>
+        <v>-6.100807631010754</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.604074504163322</v>
+        <v>0.6759994992108633</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.13958631717643</v>
+        <v>-0.9597738295575767</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.432927185623055</v>
+        <v>2.540814678194367</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.689208895810287</v>
+        <v>-6.509396408191432</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4394005373058096</v>
+        <v>0.511325532353351</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.548175094357108</v>
+        <v>-1.368362606738255</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.186535463329407</v>
+        <v>2.294422955900719</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.96578499612612</v>
+        <v>-6.785972508507265</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3239555296509371</v>
+        <v>0.3958805246984785</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.548175094357108</v>
+        <v>-1.368362606738255</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.181720895800868</v>
+        <v>2.28960838837218</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.382176870413117</v>
+        <v>-7.202364382794262</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1553928305450154</v>
+        <v>0.2273178255925572</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.548175094357108</v>
+        <v>-1.368362606738255</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.179714946409745</v>
+        <v>2.287602438981057</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.626448271140187</v>
+        <v>-7.446635783521332</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.06794296092286656</v>
+        <v>0.1398679559704084</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.548175094357108</v>
+        <v>-1.368362606738255</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.189973637078424</v>
+        <v>2.297861129649736</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.831699290376947</v>
+        <v>-7.651886802758092</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.01805788162614208</v>
+        <v>0.05386711342139927</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.548175094357108</v>
+        <v>-1.368362606738255</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.186073202224119</v>
+        <v>2.293960694795431</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.99527916856133</v>
+        <v>-7.815466680942476</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.0850849128448945</v>
+        <v>-0.01315991779735315</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.548175094357108</v>
+        <v>-1.368362606738255</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.18447812227912</v>
+        <v>2.292365614850432</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.291940510371528</v>
+        <v>-8.112128022752675</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.1999704736397656</v>
+        <v>-0.1280454785922243</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.616918230090987</v>
+        <v>-1.437105742472134</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.147011216768001</v>
+        <v>2.254898709339313</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.478660218680831</v>
+        <v>-8.298847731061977</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.27868466149789</v>
+        <v>-0.2067596664503486</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.616918230090987</v>
+        <v>-1.437105742472134</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.142984912233598</v>
+        <v>2.25087240480491</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.861661607423462</v>
+        <v>-8.681849119804609</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4319873183165264</v>
+        <v>-0.360062323268985</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.616918230090987</v>
+        <v>-1.437105742472134</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.142882810912014</v>
+        <v>2.250770303483326</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.043531398408497</v>
+        <v>-8.863718910789643</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5021637187391104</v>
+        <v>-0.4302387236915686</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.798788021076022</v>
+        <v>-1.618975533457169</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.036332452292423</v>
+        <v>2.144219944863735</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.403061720912499</v>
+        <v>-9.223249233293645</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6406255444426607</v>
+        <v>-0.5687005493951194</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.798788021076022</v>
+        <v>-1.618975533457169</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.041682755590473</v>
+        <v>2.149570248161785</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.453410784366721</v>
+        <v>-9.273598296747867</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6528491498671722</v>
+        <v>-0.5809241548196304</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.849137084530244</v>
+        <v>-1.669324596911391</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.019389337475118</v>
+        <v>2.12727683004643</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.551030061788117</v>
+        <v>-9.371217574169263</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.6888551102139617</v>
+        <v>-0.6169301151664199</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.946756361951641</v>
+        <v>-1.766943874332787</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.963859521644048</v>
+        <v>2.07174701421536</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.69855614979376</v>
+        <v>-9.518743662174906</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7449719890946467</v>
+        <v>-0.6730469940471049</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.094282449957284</v>
+        <v>-1.914469962338431</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.878237425162234</v>
+        <v>1.986124917733546</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.76197020833151</v>
+        <v>-9.72300183750477</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.7648244153911046</v>
+        <v>-0.7492370670604083</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.215858085819809</v>
+        <v>-2.04210890695242</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.810805240763362</v>
+        <v>1.915054748083795</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.836303184591674</v>
+        <v>-9.797334813764934</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.7900750514107342</v>
+        <v>-0.7744877030800379</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.360557609754482</v>
+        <v>-2.186808430887092</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.728468080886994</v>
+        <v>1.832717588207428</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.762833352924225</v>
+        <v>-9.846098735809335</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.7453154172503336</v>
+        <v>-0.7786215704043773</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.287087778087033</v>
+        <v>-2.235572352931494</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.787921681380885</v>
+        <v>1.818830936474208</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.937957770310769</v>
+        <v>-10.02122315319588</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8008099634574339</v>
+        <v>-0.8341161166114777</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.462212195473577</v>
+        <v>-2.410696770318038</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.697402251696475</v>
+        <v>1.728311506789799</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.17240986432526</v>
+        <v>-10.25567524721037</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.901809965964826</v>
+        <v>-0.9351161191188697</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.462212195473577</v>
+        <v>-2.410696770318038</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.690183086794879</v>
+        <v>1.721092341888202</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.2767845953517</v>
+        <v>-10.36004997823681</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.9502320491493808</v>
+        <v>-0.9835382023034245</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.566586926500023</v>
+        <v>-2.515071501344484</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.620886057405035</v>
+        <v>1.651795312498359</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.32957075095203</v>
+        <v>-10.41283613383714</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.9702307215509549</v>
+        <v>-1.003536874704999</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.66226241308242</v>
+        <v>-2.610746987926881</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.564596555294153</v>
+        <v>1.595505810387477</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.45560754432032</v>
+        <v>-10.53887292720543</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.017951710269156</v>
+        <v>-1.0512578634232</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.637010790272678</v>
+        <v>-2.585495365117138</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.582441257609114</v>
+        <v>1.613350512702437</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.40359203035151</v>
+        <v>-10.48685741323662</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.99315516899523</v>
+        <v>-1.026461322149274</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.637010790272678</v>
+        <v>-2.585495365117138</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.586431593295514</v>
+        <v>1.617340848388838</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.54526387207563</v>
+        <v>-10.62852925496074</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.05129913258362</v>
+        <v>-1.084605285737664</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.637010790272678</v>
+        <v>-2.585495365117138</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.584956366396773</v>
+        <v>1.615865621490096</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.49567302765079</v>
+        <v>-10.5789384105359</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.016409384648814</v>
+        <v>-1.049715537802858</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.587419945847844</v>
+        <v>-2.535904520692304</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.629764283216545</v>
+        <v>1.660673538309869</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.48286563464602</v>
+        <v>-10.56613101753113</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.024337561093587</v>
+        <v>-1.057643714247631</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.636275720856745</v>
+        <v>-2.584760295701205</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.587399684564522</v>
+        <v>1.618308939657845</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.25702048192661</v>
+        <v>-10.34028586481172</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.9244204269696144</v>
+        <v>-0.9577265801236581</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.594349045269581</v>
+        <v>-2.542833620114042</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.622134762953028</v>
+        <v>1.653044018046352</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.13244182558902</v>
+        <v>-10.21570720847413</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.8734498198785183</v>
+        <v>-0.9067559730325621</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.594349045269581</v>
+        <v>-2.542833620114042</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.623273907509087</v>
+        <v>1.654183162602411</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.1853371136333</v>
+        <v>-10.26860249651841</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.8919741609341258</v>
+        <v>-0.9252803140881696</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.589393699181135</v>
+        <v>-2.537878274025596</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.628880889324263</v>
+        <v>1.659790144417586</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.11320393834542</v>
+        <v>-10.19646932123053</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8573871865803371</v>
+        <v>-0.8906933397343808</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.589393699181135</v>
+        <v>-2.537878274025596</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.634614593562899</v>
+        <v>1.665523848656223</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.04183754573578</v>
+        <v>-10.12510292862089</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8385778919303428</v>
+        <v>-0.8718840450843865</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.518027306571487</v>
+        <v>-2.466511881415947</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.667697166734823</v>
+        <v>1.698606421828146</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.948378511750551</v>
+        <v>-10.03164389463566</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.811077759649161</v>
+        <v>-0.8443839128032047</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.518027306571487</v>
+        <v>-2.466511881415947</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.657813685421915</v>
+        <v>1.688722940515239</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.681136710882154</v>
+        <v>-9.764402093767263</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7060155998011752</v>
+        <v>-0.739321752955219</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.518027306571487</v>
+        <v>-2.466511881415947</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.655979124922542</v>
+        <v>1.686888380015865</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.583229672205663</v>
+        <v>-9.666495055090772</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.66715309930404</v>
+        <v>-0.7004592524580837</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.45004155671093</v>
+        <v>-2.398526131555391</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.696470259865415</v>
+        <v>1.727379514958738</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.559276131229705</v>
+        <v>-9.642541514114814</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.656903176768163</v>
+        <v>-0.6902093299222067</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.426088015734973</v>
+        <v>-2.374572590579433</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.711510890596483</v>
+        <v>1.742420145689806</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.295216192906908</v>
+        <v>-9.378481575792017</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5645395176007968</v>
+        <v>-0.5978456707548405</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.162028077412177</v>
+        <v>-2.110512652256638</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.856686537428408</v>
+        <v>1.887595792521732</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.588136569402071</v>
+        <v>-8.67140195228718</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2844947018591624</v>
+        <v>-0.3178008550132061</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.162028077412177</v>
+        <v>-2.110512652256638</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.853899503768107</v>
+        <v>1.884808758861431</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.54795227103588</v>
+        <v>-8.63121765392099</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2680773586248448</v>
+        <v>-0.3013835117788886</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.121843779045986</v>
+        <v>-2.070328353890447</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.878353706675663</v>
+        <v>1.909262961768987</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.384552400096517</v>
+        <v>-8.467817782981626</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2033505890283429</v>
+        <v>-0.2366567421823866</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.958443908106624</v>
+        <v>-1.906928482951084</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.975760450460037</v>
+        <v>2.006669705553361</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.151071177866918</v>
+        <v>-8.234336560752027</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1020336712986505</v>
+        <v>-0.1353398244526942</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.724962685877025</v>
+        <v>-1.673447260721486</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.123773612635649</v>
+        <v>2.154682867728973</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.001404786859403</v>
+        <v>-8.084670169744513</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.04505932520860378</v>
+        <v>-0.07836547836264796</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.632059194634489</v>
+        <v>-1.58054376947895</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.176623497068212</v>
+        <v>2.207532752161535</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.869129313228517</v>
+        <v>-7.952394696113626</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.003218350990777719</v>
+        <v>-0.03008780216326601</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.499783721003602</v>
+        <v>-1.448268295848063</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.251356267993771</v>
+        <v>2.282265523087094</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.678529638555364</v>
+        <v>-7.761795021440474</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.08227328154767566</v>
+        <v>0.04896712839363149</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.30918404633045</v>
+        <v>-1.25766862117491</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.368531133485299</v>
+        <v>2.399440388578622</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.429529839871783</v>
+        <v>-7.512795222756893</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1947795422447669</v>
+        <v>0.1614733890907227</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.30918404633045</v>
+        <v>-1.25766862117491</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.381437474708958</v>
+        <v>2.412346729802281</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.535119829644888</v>
+        <v>-7.618385212529997</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.02456761673630625</v>
+        <v>-0.008738536417737919</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.414774036103554</v>
+        <v>-1.363258610948014</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.190107551245876</v>
+        <v>2.2210168063392</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.553854731763485</v>
+        <v>-7.637120114648594</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.06561799776595389</v>
+        <v>0.03231184461190972</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.420370045763685</v>
+        <v>-1.368854620608146</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.235294287326884</v>
+        <v>2.266203542420207</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.405914690355885</v>
+        <v>-7.489180073240995</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.004915091640826041</v>
+        <v>-0.02839106151321813</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.400049129855128</v>
+        <v>-1.348533704699588</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.127607914183851</v>
+        <v>2.158517169277175</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.352945168101897</v>
+        <v>-7.436210550987006</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.01738891428894318</v>
+        <v>-0.01591723886510099</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.347079607601139</v>
+        <v>-1.295564182445599</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.150675641282766</v>
+        <v>2.18158489637609</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.309396761331207</v>
+        <v>-7.392662144216316</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.0278476649021262</v>
+        <v>-0.00545848825191797</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.347079607601139</v>
+        <v>-1.295564182445599</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.143715029187673</v>
+        <v>2.174624284280997</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.067248367877348</v>
+        <v>-7.150513750762458</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1391693766648125</v>
+        <v>0.1058632235107684</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.347079607601139</v>
+        <v>-1.295564182445599</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.158177383568816</v>
+        <v>2.18908663866214</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.958989230754827</v>
+        <v>-7.042254613639936</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1770051519730163</v>
+        <v>0.1436989988189721</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.347079607601139</v>
+        <v>-1.295564182445599</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.152709504028011</v>
+        <v>2.183618759121335</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.835698095937696</v>
+        <v>-6.918963478822805</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2238196999104454</v>
+        <v>0.1905135467564016</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.223788472784008</v>
+        <v>-1.172273047628469</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.224182278928866</v>
+        <v>2.25509153402219</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.814548897034252</v>
+        <v>-6.897814279919362</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2399803577091482</v>
+        <v>0.206674204555104</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.202639273880565</v>
+        <v>-1.151123848725025</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.244572776508257</v>
+        <v>2.275482031601581</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.570783455050808</v>
+        <v>-6.654048837935918</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3332672428495767</v>
+        <v>0.2999610896955325</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.202639273880565</v>
+        <v>-1.151123848725025</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.240353484855308</v>
+        <v>2.271262739948632</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.469020634773513</v>
+        <v>-6.552286017658623</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3760966848805105</v>
+        <v>0.3427905317264663</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.189420205488136</v>
+        <v>-1.137904780332597</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.250409239810781</v>
+        <v>2.281318494904105</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.219170240824439</v>
+        <v>-6.302435623709548</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4687789174438426</v>
+        <v>0.4354727642897984</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.189420205488136</v>
+        <v>-1.137904780332597</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.243151314794483</v>
+        <v>2.274060569887807</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.043278148357007</v>
+        <v>-6.126543531242115</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5427348779514638</v>
+        <v>0.5094287247974201</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.189420205488136</v>
+        <v>-1.137904780332597</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.246750438315132</v>
+        <v>2.277659693408456</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.871831685334543</v>
+        <v>-5.955097068219652</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6246409692150032</v>
+        <v>0.5913348160609595</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.017973742465673</v>
+        <v>-0.9664583173101337</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.362945822183164</v>
+        <v>2.393855077276487</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.797542119596204</v>
+        <v>-5.880807502481312</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6533772731266358</v>
+        <v>0.6200711199725921</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9436841767273336</v>
+        <v>-0.8921687515717944</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.406540039242465</v>
+        <v>2.437449294335788</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.73390637736227</v>
+        <v>-5.817171760247378</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6835263710745267</v>
+        <v>0.650220217920483</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8800484344933991</v>
+        <v>-0.8285330093378599</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.449416285637143</v>
+        <v>2.480325540730466</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.622479618036349</v>
+        <v>-5.705745000921458</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7092913335886903</v>
+        <v>0.6759851804346466</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8800484344933991</v>
+        <v>-0.8285330093378599</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.430610544420938</v>
+        <v>2.461519799514261</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.382049121231489</v>
+        <v>-5.465314504116598</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8072066089355121</v>
+        <v>0.7739004557814684</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6396179376885388</v>
+        <v>-0.5881025125329996</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.576611919128732</v>
+        <v>2.607521174222055</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.309806553060294</v>
+        <v>-5.393071935945403</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8400329500388102</v>
+        <v>0.8067267968847665</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6396179376885388</v>
+        <v>-0.5881025125329996</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.580541232963552</v>
+        <v>2.611450488056875</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.256808230778907</v>
+        <v>-5.340073613664015</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8619108628687053</v>
+        <v>0.8286047097146616</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5842816786866</v>
+        <v>-0.5327662535310608</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.614421572282055</v>
+        <v>2.645330827375378</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.14800334529918</v>
+        <v>-5.231268728184288</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9024308882805894</v>
+        <v>0.8691247351265456</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5842816786866</v>
+        <v>-0.5327662535310608</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.611419643502049</v>
+        <v>2.642328898595372</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.927982547262169</v>
+        <v>-5.011247930147277</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.992018244506008</v>
+        <v>0.958712091351964</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4430618336186197</v>
+        <v>-0.3915464084630805</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.697730587553451</v>
+        <v>2.728639842646774</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.795114858198891</v>
+        <v>-4.878380241084</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.061059502933142</v>
+        <v>1.027753349779098</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4430618336186197</v>
+        <v>-0.3915464084630805</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.713624770355274</v>
+        <v>2.744534025448598</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.674941774834393</v>
+        <v>-4.758207157719501</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.110274580719244</v>
+        <v>1.0769684275652</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.3228887502541208</v>
+        <v>-0.2713733250985816</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.786874464814276</v>
+        <v>2.817783719907599</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.530269629734655</v>
+        <v>-4.613535012619764</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.178231541320578</v>
+        <v>1.144925388166535</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1782166051543834</v>
+        <v>-0.1267011799988442</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.883765854435558</v>
+        <v>2.914675109528881</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.590144457092348</v>
+        <v>-4.673409839977456</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.140319101778927</v>
+        <v>1.107012948624884</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2380914325120755</v>
+        <v>-0.1865760073565363</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.833878449422368</v>
+        <v>2.864787704515692</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674515</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.503344959313339</v>
+        <v>-4.586610342198448</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.197439394213097</v>
+        <v>1.164133241059053</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2380914325120755</v>
+        <v>-0.1865760073565363</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.856278942744934</v>
+        <v>2.887188197838258</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430694</v>
+        <v>3.729146398430695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.505814665775145</v>
+        <v>-4.589080048660254</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.196523913001787</v>
+        <v>1.163217759847743</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.2405611389738816</v>
+        <v>-0.1890457138183425</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.854869520241263</v>
+        <v>2.885778775334586</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.574184852099155</v>
+        <v>-4.657450234984264</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.180182760946884</v>
+        <v>1.146876607792841</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.2312854399376667</v>
+        <v>-0.1797700147821275</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.871441862137694</v>
+        <v>2.902351117231017</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.682723033015289</v>
+        <v>-4.765988415900398</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.127204197212322</v>
+        <v>1.093898044058278</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.2312854399376667</v>
+        <v>-0.1797700147821275</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.861878570769585</v>
+        <v>2.892787825862909</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.713716192343995</v>
+        <v>-4.796981575229103</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9395164985212268</v>
+        <v>0.906210345367183</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.2312854399376667</v>
+        <v>-0.1797700147821275</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.686588135809972</v>
+        <v>2.717497390903295</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.538241932551526</v>
+        <v>-4.621507315436634</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.014273434430002</v>
+        <v>0.9809672812759584</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.2312854399376667</v>
+        <v>-0.1797700147821275</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.69115536780176</v>
+        <v>2.722064622895083</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.649178185192775</v>
+        <v>-4.732443568077883</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9456409621347097</v>
+        <v>0.912334808980666</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.2312854399376667</v>
+        <v>-0.1797700147821275</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.666897396562967</v>
+        <v>2.69780665165629</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.615514639720493</v>
+        <v>-4.698780022605601</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9622377655435281</v>
+        <v>0.9289316123894844</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.1976218944653849</v>
+        <v>-0.1461064693098457</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.690226909066241</v>
+        <v>2.721136164159565</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.555662020516769</v>
+        <v>-4.638927403401878</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9963511996571497</v>
+        <v>0.963045046503106</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.1976218944653849</v>
+        <v>-0.1461064693098457</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.700399295498374</v>
+        <v>2.731308550591697</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.469418557490392</v>
+        <v>-4.5526839403755</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.025794855441561</v>
+        <v>0.9924887022875173</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.1976218944653849</v>
+        <v>-0.1461064693098457</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.695345566072234</v>
+        <v>2.726254821165558</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.514725376889372</v>
+        <v>-4.59799075977448</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9994479031264947</v>
+        <v>0.9661417499724509</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2384320574746157</v>
+        <v>-0.1869166323190765</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.662635243711221</v>
+        <v>2.693544498804544</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.543758481591673</v>
+        <v>-4.627023864476781</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9883865342786757</v>
+        <v>0.955080381124632</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2384320574746157</v>
+        <v>-0.1869166323190765</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.663187116744323</v>
+        <v>2.694096371837646</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.450948000140813</v>
+        <v>-4.534213383025921</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9547834187503854</v>
+        <v>0.9214772655963417</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1456215760237563</v>
+        <v>-0.09410615086821711</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.648146097506204</v>
+        <v>2.679055352599527</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.495337469470241</v>
+        <v>-4.578602852355349</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9389011069432152</v>
+        <v>0.9055949537891714</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.190011045353184</v>
+        <v>-0.1384956201976448</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.623385891833148</v>
+        <v>2.654295146926472</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.38266625123399</v>
+        <v>-4.465931634119099</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9790453027494381</v>
+        <v>0.9457391495953944</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.07733982711693377</v>
+        <v>-0.02582440196139457</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.686064331286621</v>
+        <v>2.716973586379945</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.270289250051317</v>
+        <v>-4.353554632936426</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.029487399053175</v>
+        <v>0.9961812458991308</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.07733982711693377</v>
+        <v>-0.02582440196139457</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.691555627117288</v>
+        <v>2.722464882210612</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.29806964795267</v>
+        <v>-4.381335030837779</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.029872441661173</v>
+        <v>0.9965662885071289</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1051202250182868</v>
+        <v>-0.05360479986274763</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.686384590145016</v>
+        <v>2.71729384523834</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.381070928977949</v>
+        <v>-4.464336311863057</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8350276492517144</v>
+        <v>0.8017214960976706</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1236911095454606</v>
+        <v>-0.07217568438992139</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.513597779429365</v>
+        <v>2.544507034522688</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.48968500742128</v>
+        <v>-4.572950390306389</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9117316785935876</v>
+        <v>0.8784255254395439</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1236911095454606</v>
+        <v>-0.07217568438992139</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.633747440148571</v>
+        <v>2.664656695241894</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.576283590402383</v>
+        <v>-4.659548973287492</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8916052715034692</v>
+        <v>0.8582991183494255</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1236911095454606</v>
+        <v>-0.07217568438992139</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.648260466250894</v>
+        <v>2.679169721344217</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.537899927844232</v>
+        <v>-4.62116531072934</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9043781778690985</v>
+        <v>0.8710720247150547</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.08530744698730941</v>
+        <v>-0.03379202183177021</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.668710105128153</v>
+        <v>2.699619360221476</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.360783597809066</v>
+        <v>-4.444048980694174</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9719537387284669</v>
+        <v>0.9386475855744232</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.08530744698730941</v>
+        <v>-0.03379202183177021</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.665439133973455</v>
+        <v>2.696348389066778</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.405875842642612</v>
+        <v>-4.48914122552772</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9546002325569616</v>
+        <v>0.9212940794029179</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1472034901566992</v>
+        <v>-0.09568806500116001</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.628984899833734</v>
+        <v>2.659894154927057</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.226500421403844</v>
+        <v>-4.309765804288952</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.020137376358883</v>
+        <v>0.9868312232048393</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.009573268014019476</v>
+        <v>0.06108869316955867</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.716837930042579</v>
+        <v>2.747747185135903</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.27151463492445</v>
+        <v>-4.354780017809558</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9829391462822306</v>
+        <v>0.9496329931281868</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.02077562730058513</v>
+        <v>0.03073979785495407</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.679436048185407</v>
+        <v>2.71034530327873</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.538519145196885</v>
+        <v>-4.621784528081993</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8818289045122023</v>
+        <v>0.8485227513581586</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2151386653435337</v>
+        <v>-0.1636232401879945</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.568509787698583</v>
+        <v>2.599419042791907</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.639716926634057</v>
+        <v>-4.722982309519166</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8405537138338346</v>
+        <v>0.8072475606797909</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2835474788888529</v>
+        <v>-0.2320320537333137</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.526668421467893</v>
+        <v>2.557577676561217</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.607241340463285</v>
+        <v>-4.690506723348394</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8511439098564602</v>
+        <v>0.8178377567024164</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2835474788888529</v>
+        <v>-0.2320320537333137</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.52426838302221</v>
+        <v>2.555177638115533</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.588203212755988</v>
+        <v>-4.671468595641096</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8552838801476241</v>
+        <v>0.8219777269935804</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3417310902200474</v>
+        <v>-0.2902156650645082</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.485882935431738</v>
+        <v>2.516792190525062</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.619329843906606</v>
+        <v>-4.702595226791715</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.020415096626057</v>
+        <v>0.9871089434720135</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3417310902200474</v>
+        <v>-0.2902156650645082</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.663464804370419</v>
+        <v>2.694374059463742</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.633196605240524</v>
+        <v>-4.716461988125633</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.015701721078624</v>
+        <v>0.9823955679245799</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3795890069538704</v>
+        <v>-0.3280735817983312</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.641583383316258</v>
+        <v>2.672492638409582</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.653453903769482</v>
+        <v>-4.736719286654591</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.013607332063966</v>
+        <v>0.9803011789099227</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.3795890069538704</v>
+        <v>-0.3280735817983312</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.647591913713184</v>
+        <v>2.678501168806508</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.50571093353448</v>
+        <v>-4.588976316419588</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.151857167949989</v>
+        <v>1.118551014795946</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2117816497189872</v>
+        <v>-0.160266224563448</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.827428975846136</v>
+        <v>2.858338230939459</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.607725616065701</v>
+        <v>-4.690990998950809</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.113844916468982</v>
+        <v>1.080538763314938</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2117816497189872</v>
+        <v>-0.160266224563448</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.830222597377617</v>
+        <v>2.86113185247094</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.601572910012917</v>
+        <v>-4.684838292898025</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.116968347281754</v>
+        <v>1.08366219412771</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2056289436662029</v>
+        <v>-0.1541135185106637</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.834576569400946</v>
+        <v>2.865485824494269</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.618382208163418</v>
+        <v>-4.701647591048527</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.109325104761663</v>
+        <v>1.07601895160762</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.2224382418167046</v>
+        <v>-0.1709228166611654</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.823571467250755</v>
+        <v>2.854480722344079</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.556084209387296</v>
+        <v>-4.639349592272405</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.200579858068933</v>
+        <v>1.167273704914889</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.2224382418167046</v>
+        <v>-0.1709228166611654</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.889907021047576</v>
+        <v>2.9208162761409</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.354294011722138</v>
+        <v>-4.437559394607247</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9898768095243944</v>
+        <v>0.9565706563703507</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.02442004964755018</v>
+        <v>0.02709537550798902</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.717298808738467</v>
+        <v>2.748208063831791</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.294403330079545</v>
+        <v>-4.377668712964653</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.084123314503607</v>
+        <v>1.050817161349563</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.0354706319950433</v>
+        <v>0.0869860571505825</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.823523450046198</v>
+        <v>2.854432705139522</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.392143874704519</v>
+        <v>-4.475409257589628</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.059654832769661</v>
+        <v>1.026348679615617</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.01958135386206311</v>
+        <v>0.07109677901760231</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.828617619282454</v>
+        <v>2.859526874375777</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.568481634827449</v>
+        <v>-4.651747017712557</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9876557095451608</v>
+        <v>0.9543495563911171</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.1567564062608663</v>
+        <v>-0.1052409811053271</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.721350944033368</v>
+        <v>2.752260199126691</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.492059588395522</v>
+        <v>-4.57532497128063</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.01671614615786</v>
+        <v>0.9834099930038163</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.1567564062608663</v>
+        <v>-0.1052409811053271</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.719842562073296</v>
+        <v>2.75075181716662</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.447686456756953</v>
+        <v>-4.530951839642062</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.034328266248724</v>
+        <v>1.00102211309468</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.1123832746222977</v>
+        <v>-0.06086784946675849</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.746329308491874</v>
+        <v>2.777238563585197</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.439732486462181</v>
+        <v>-4.522997869347289</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.037509854366633</v>
+        <v>1.004203701212589</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.1123832746222977</v>
+        <v>-0.06086784946675849</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.746329308491874</v>
+        <v>2.777238563585197</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.392076755901125</v>
+        <v>-4.475342138786234</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.06295390361886</v>
+        <v>1.029647750464816</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.06472754406124204</v>
+        <v>-0.01321211890570284</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.781304503856312</v>
+        <v>2.812213758949635</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.264392446106829</v>
+        <v>-4.416567442210528</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.118920000911303</v>
+        <v>1.058050002469823</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.06295676573305442</v>
+        <v>0.04556257767000216</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.862807463107614</v>
+        <v>2.852370950269783</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.325059036509217</v>
+        <v>-4.477234032612918</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.08140803722622</v>
+        <v>1.020538038784739</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.01874155098547925</v>
+        <v>-0.03613573904853151</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.800543145552366</v>
+        <v>2.790106632714535</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.280220634900819</v>
+        <v>-4.432395631004519</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.103441100480208</v>
+        <v>1.042571102038727</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.01419811804060978</v>
+        <v>-0.03159230610366204</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.807366907929917</v>
+        <v>2.796930395092085</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.380979270657817</v>
+        <v>-4.533154266761517</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.067298585808486</v>
+        <v>1.006428587367006</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.1030236867676152</v>
+        <v>-0.1204178748306675</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.758232506324791</v>
+        <v>2.74779599348696</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.336776433571917</v>
+        <v>-4.488951429675617</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.090859323170684</v>
+        <v>1.029989324729203</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.05882084968171475</v>
+        <v>-0.07621503774476701</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.790633811104169</v>
+        <v>2.780197298266337</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.373755461235359</v>
+        <v>-4.52593045733906</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.074477712574554</v>
+        <v>1.013607714133074</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.02184694789038422</v>
+        <v>-0.03924113595343648</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.811228152648215</v>
+        <v>2.800791639810383</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.3938135401002</v>
+        <v>-4.5459885362039</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.117702246211658</v>
+        <v>1.056832247770177</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.02184694789038422</v>
+        <v>-0.03924113595343648</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.862475917831254</v>
+        <v>2.852039404993423</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.35388286692231</v>
+        <v>-4.50605786302601</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.132115220077067</v>
+        <v>1.071245221635586</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.01808372528750612</v>
+        <v>0.0006895372244538622</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.884875026332241</v>
+        <v>2.87443851349441</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.302850774199782</v>
+        <v>-4.455025770303482</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.147476285404348</v>
+        <v>1.086606286962867</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.06911581801003408</v>
+        <v>0.05172162994698182</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.910442510204029</v>
+        <v>2.900005997366197</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.237626593072576</v>
+        <v>-4.389801589176277</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.190753361947935</v>
+        <v>1.129883363506454</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.1343399991372397</v>
+        <v>0.1169458110741874</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.966764422973057</v>
+        <v>2.956327910135225</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.200199573001442</v>
+        <v>-4.352374569105143</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.201685142275669</v>
+        <v>1.140815143834188</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.1395915371664214</v>
+        <v>0.1221973491033691</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.965876318089846</v>
+        <v>2.955439805252015</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.220311229036151</v>
+        <v>-4.372486225139851</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.194897272193026</v>
+        <v>1.134027273751546</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.1506188821638406</v>
+        <v>0.1332246941007883</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.973749517419538</v>
+        <v>2.963313004581706</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.166566414608946</v>
+        <v>-4.318741410712646</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.376952968985119</v>
+        <v>1.316082970543638</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.1606821916043025</v>
+        <v>0.1432880035412503</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.140345274105026</v>
+        <v>3.129908761267195</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.142774846002804</v>
+        <v>-4.294949842106504</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.506582505645393</v>
+        <v>1.445712507203912</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.1844737602104448</v>
+        <v>0.1670795721473926</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.274733124486529</v>
+        <v>3.264296611648697</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.116690761738996</v>
+        <v>-4.268865757842696</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.508724115364775</v>
+        <v>1.447854116923295</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.1844737602104448</v>
+        <v>0.1670795721473926</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.266441100500387</v>
+        <v>3.256004587662556</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.015845863498491</v>
+        <v>-4.264531454785648</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.547255270244756</v>
+        <v>1.447781033729893</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.3969725277772699</v>
+        <v>0.3187296754665965</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.392133556624262</v>
+        <v>3.345187845237858</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.006953402105208</v>
+        <v>-4.255638993392365</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.568366660528861</v>
+        <v>1.468892424013998</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.3969725277772699</v>
+        <v>0.3187296754665965</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.409687962351053</v>
+        <v>3.362742250964649</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.175429519075085</v>
+        <v>-4.424115110362242</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.492831261145494</v>
+        <v>1.393357024630631</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.3690246920606891</v>
+        <v>0.2907818397500157</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.384774308325689</v>
+        <v>3.337828596939285</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.233772154546119</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.477629990213502</v>
+        <v>-3.726315581500659</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.842363734146971</v>
+        <v>1.742889497632108</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.2986766326902784</v>
+        <v>0.220433780379605</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.412978134160286</v>
+        <v>3.366032422773882</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.224436177043023</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.45490888653035</v>
+        <v>-3.703594477817507</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.842116198117136</v>
+        <v>1.742641961602273</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.2986766326902784</v>
+        <v>0.220433780379605</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.40364215665719</v>
+        <v>3.356696445270786</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.383342302894192</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.595201486067542</v>
+        <v>-3.843887077354699</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.944905284153428</v>
+        <v>1.845431047638565</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.1583840331530857</v>
+        <v>0.08014118084241234</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.478372722786044</v>
+        <v>3.43142701139964</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.420420125387839</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.749982492845797</v>
+        <v>-3.998668084132954</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.920070703935773</v>
+        <v>1.82059646742091</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.1250163590986096</v>
+        <v>0.04677350678793624</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.495429940847005</v>
+        <v>3.448484229460601</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.417095481377384</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.817242936867714</v>
+        <v>-4.234778905308041</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.889841882316551</v>
+        <v>1.72282749494042</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.05775591507669253</v>
+        <v>-0.1893373143871505</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.4517490304234</v>
+        <v>3.303493092745094</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.849137925783207</v>
+        <v>3.451087042262799</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.507800395636292</v>
+        <v>3.266584865068838</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.817242936867714</v>
+        <v>-4.157600945643908</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.889841882316551</v>
+        <v>1.603188062497528</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.05775591507669253</v>
+        <v>-0.1121593547230164</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.50086419262266</v>
+        <v>3.199289252235029</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240621.xlsx
+++ b/tame_output/ON/bt/strategyON_20240621.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.1%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>52.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>74.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,37 +844,37 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>59.1%</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>29.7%</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>54.4%</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>29.9%</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>1.8</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>31.1%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.7%</t>
+          <t>-75.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.7%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.1%</t>
+          <t>123.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.9%</t>
+          <t>94.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-665.2%</t>
+          <t>-675.7%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.6%</t>
+          <t>-51.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.8%</t>
+          <t>-71.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.1%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>429.3%</t>
+          <t>449.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.0%</t>
+          <t>-10.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-577.3%</t>
+          <t>-567.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-266.5%</t>
+          <t>-270.7%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-35.1%</t>
+          <t>-33.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-215.9%</t>
+          <t>-196.0%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-24.0%</t>
+          <t>-24.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-273.7%</t>
+          <t>-291.7%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-30.9%</t>
+          <t>-31.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-17.7%</t>
+          <t>-17.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-29.3%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-171.8%</t>
+          <t>-196.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-235.2%</t>
+          <t>-233.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>95.8%</t>
+          <t>96.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-164.6%</t>
+          <t>-175.4%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.8%</t>
+          <t>-28.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-126.1%</t>
+          <t>-108.8%</t>
         </is>
       </c>
     </row>
@@ -43733,16 +43733,16 @@
         <v>3.13991794227561</v>
       </c>
       <c r="D1834" t="n">
-        <v>0.9296086660691371</v>
+        <v>0.7497961784502833</v>
       </c>
       <c r="E1834" t="n">
-        <v>3.511404984389518</v>
+        <v>3.439479989341976</v>
       </c>
       <c r="F1834" t="n">
-        <v>1.811577112298561</v>
+        <v>1.631764624679707</v>
       </c>
       <c r="G1834" t="n">
-        <v>4.226864209654747</v>
+        <v>4.118976717083434</v>
       </c>
     </row>
     <row r="1835">
@@ -43756,16 +43756,16 @@
         <v>3.138175778137954</v>
       </c>
       <c r="D1835" t="n">
-        <v>0.7330582550159315</v>
+        <v>0.5532457673970779</v>
       </c>
       <c r="E1835" t="n">
-        <v>3.43104265583058</v>
+        <v>3.359117660783038</v>
       </c>
       <c r="F1835" t="n">
-        <v>1.848231277987064</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1835" t="n">
-        <v>4.247114544930193</v>
+        <v>4.139227052358882</v>
       </c>
     </row>
     <row r="1836">
@@ -43779,16 +43779,16 @@
         <v>3.118001050765402</v>
       </c>
       <c r="D1836" t="n">
-        <v>0.5795388705304668</v>
+        <v>0.3997263829116132</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.349460174663841</v>
+        <v>3.2775351796163</v>
       </c>
       <c r="F1836" t="n">
-        <v>1.885197752456588</v>
+        <v>1.705385264837735</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.249119702239355</v>
+        <v>4.141232209668043</v>
       </c>
     </row>
     <row r="1837">
@@ -43802,16 +43802,16 @@
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.3975323072074982</v>
+        <v>0.2921741282647279</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.277146688060528</v>
+        <v>3.23500341648342</v>
       </c>
       <c r="F1837" t="n">
-        <v>1.885197752456588</v>
+        <v>1.705385264837735</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.249608840965229</v>
+        <v>4.141721348393917</v>
       </c>
     </row>
     <row r="1838">
@@ -43825,16 +43825,16 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.3493100403604147</v>
+        <v>0.2439518614176444</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.261937763943361</v>
+        <v>3.219794492366253</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.836975485609505</v>
+        <v>1.657162997990651</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.224755463478646</v>
+        <v>4.116867970907334</v>
       </c>
     </row>
     <row r="1839">
@@ -43848,16 +43848,16 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.1121785485106196</v>
+        <v>0.00682036956784926</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.202026251700985</v>
+        <v>3.159882980123877</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.836975485609505</v>
+        <v>1.657162997990651</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.259696547976187</v>
+        <v>4.151809055404875</v>
       </c>
     </row>
     <row r="1840">
@@ -43871,16 +43871,16 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.1172161392382061</v>
+        <v>0.01185796029543579</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.202618728177358</v>
+        <v>3.16047545660025</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.892619941875822</v>
+        <v>1.712807454256969</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.291660661921316</v>
+        <v>4.183773169350004</v>
       </c>
     </row>
     <row r="1841">
@@ -43888,22 +43888,22 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082123</v>
+        <v>3.299560092082124</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.1399778954698506</v>
+        <v>-0.245336074412621</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.078487495917872</v>
+        <v>3.036344224340764</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.635425907167765</v>
+        <v>1.455613419548912</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.116090622720219</v>
+        <v>4.008203130148907</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.2057452855192627</v>
+        <v>-0.311103464462033</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.053198149028577</v>
+        <v>3.011054877451469</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.635425907167765</v>
+        <v>1.455613419548912</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.117108231850689</v>
+        <v>4.009220739279377</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.4109899625765073</v>
+        <v>-0.5163481415192777</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.961728310193435</v>
+        <v>2.919585038616327</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.635425907167765</v>
+        <v>1.455613419548912</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.107736263838444</v>
+        <v>3.999848771267133</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.4927618630042589</v>
+        <v>-0.5981200419470294</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.919102275977573</v>
+        <v>2.876959004400465</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.662461480573902</v>
+        <v>1.482648992955049</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.114040333837365</v>
+        <v>4.006152841266053</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.5599709708761367</v>
+        <v>-0.6653291498189071</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.896983949662524</v>
+        <v>2.854840678085416</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.662461480573902</v>
+        <v>1.482648992955049</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.118805650671067</v>
+        <v>4.010918158099756</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.7675367552677486</v>
+        <v>-0.872894934210519</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.81178243202512</v>
+        <v>2.769639160448011</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.45489569618229</v>
+        <v>1.275083208563437</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.992090976155341</v>
+        <v>3.884203483584028</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.185290778814586</v>
+        <v>-1.290648957757356</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.642607714111448</v>
+        <v>2.60046444253434</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.037141672635453</v>
+        <v>0.8573291850165997</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.739365453532302</v>
+        <v>3.631477960960989</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.475422445420017</v>
+        <v>-1.580780624362787</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.526421264068197</v>
+        <v>2.484277992491089</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.061223467375633</v>
+        <v>0.8814109797567796</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.753680746975331</v>
+        <v>3.645793254404019</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.683426503773094</v>
+        <v>-1.788784682715865</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.448111785280891</v>
+        <v>2.405968513703783</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.061223467375633</v>
+        <v>0.8814109797567796</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.758572891529257</v>
+        <v>3.650685398957944</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.89483892466107</v>
+        <v>-2.00019710360384</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.358628273263689</v>
+        <v>2.316485001686581</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.849811046487658</v>
+        <v>0.6699985588688046</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.62680689533446</v>
+        <v>3.518919402763148</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.260907651805722</v>
+        <v>-2.366265830748493</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.205285081712277</v>
+        <v>2.163141810135169</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.4837423193430054</v>
+        <v>0.3039298317241519</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.400249958354117</v>
+        <v>3.292362465782805</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.469398433257406</v>
+        <v>-2.574756612200177</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.142227058870372</v>
+        <v>2.100083787293264</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.275251537891321</v>
+        <v>0.09543905027246746</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.295493779221875</v>
+        <v>3.187606286650563</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.716599618022628</v>
+        <v>-2.821957796965399</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.051445335372852</v>
+        <v>2.009302063795744</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.2954048913901334</v>
+        <v>0.1155924037712799</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.315684541729731</v>
+        <v>3.207797049158418</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.208984646046725</v>
+        <v>-3.314342824989496</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.855597716206945</v>
+        <v>1.813454444629837</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.1969801366339634</v>
+        <v>-0.3767926242528168</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.021359916959005</v>
+        <v>2.913472424387693</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.594165036976797</v>
+        <v>-3.699523215919568</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.70006809864778</v>
+        <v>1.657924827070671</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.1969801366339634</v>
+        <v>-0.3767926242528168</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.019902455771868</v>
+        <v>2.912014963200556</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.844035716991379</v>
+        <v>-3.94939389593415</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.601888950096563</v>
+        <v>1.559745678519455</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.1607174168035001</v>
+        <v>-0.3405299044223536</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.043429211124762</v>
+        <v>2.93554171855345</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.050547493878399</v>
+        <v>-4.155905672821171</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.515390297998013</v>
+        <v>1.473247026420904</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.3672291936905216</v>
+        <v>-0.547041681309375</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.915628203648807</v>
+        <v>2.807740711077495</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.369891568958901</v>
+        <v>-4.475249747901673</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.389425594666071</v>
+        <v>1.347282323088963</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.3672291936905216</v>
+        <v>-0.547041681309375</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.917401130349067</v>
+        <v>2.809513637777755</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.801697362108689</v>
+        <v>-4.90705554105146</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.203036164873561</v>
+        <v>1.160892893296452</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.5036466901317886</v>
+        <v>-0.683459177750642</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.821883519951711</v>
+        <v>2.713996027380399</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.036391356241241</v>
+        <v>-5.141749535184013</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.09744334222263</v>
+        <v>1.055300070645522</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.4973104229025335</v>
+        <v>-0.6771229105213868</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.813970055291355</v>
+        <v>2.706082562720043</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.372054003471693</v>
+        <v>-5.477412182414465</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9617588749864145</v>
+        <v>0.9196156034093064</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.5652414083914383</v>
+        <v>-0.7450538960102917</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.771792055653977</v>
+        <v>2.663904563082665</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.735680248372007</v>
+        <v>-5.841038427314778</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8227959372605307</v>
+        <v>0.7806526656834225</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.6634630452585641</v>
+        <v>-0.8432755328774175</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.719346633767943</v>
+        <v>2.611459141196631</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.100807631010754</v>
+        <v>-6.206165809953525</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6759994992108633</v>
+        <v>0.6338562276337552</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.9597738295575767</v>
+        <v>-1.13958631717643</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.540814678194367</v>
+        <v>2.432927185623055</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.509396408191432</v>
+        <v>-6.614754587134204</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.511325532353351</v>
+        <v>0.4691822607762428</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.368362606738255</v>
+        <v>-1.548175094357108</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.294422955900719</v>
+        <v>2.186535463329407</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.785972508507265</v>
+        <v>-6.891330687450036</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3958805246984785</v>
+        <v>0.3537372531213703</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.368362606738255</v>
+        <v>-1.548175094357108</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.28960838837218</v>
+        <v>2.181720895800868</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.202364382794262</v>
+        <v>-7.307722561737034</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2273178255925572</v>
+        <v>0.1851745540154486</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.368362606738255</v>
+        <v>-1.548175094357108</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.287602438981057</v>
+        <v>2.179714946409745</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.446635783521332</v>
+        <v>-7.551993962464103</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.1398679559704084</v>
+        <v>0.09772468439329973</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.368362606738255</v>
+        <v>-1.548175094357108</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.297861129649736</v>
+        <v>2.189973637078424</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.651886802758092</v>
+        <v>-7.757244981700864</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.05386711342139927</v>
+        <v>0.01172384184429109</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.368362606738255</v>
+        <v>-1.548175094357108</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.293960694795431</v>
+        <v>2.186073202224119</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.815466680942476</v>
+        <v>-7.920824859885247</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.01315991779735315</v>
+        <v>-0.05530318937446133</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.368362606738255</v>
+        <v>-1.548175094357108</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.292365614850432</v>
+        <v>2.18447812227912</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.112128022752675</v>
+        <v>-8.217486201695445</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.1280454785922243</v>
+        <v>-0.1701887501693324</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.437105742472134</v>
+        <v>-1.616918230090987</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.254898709339313</v>
+        <v>2.147011216768001</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.298847731061977</v>
+        <v>-8.404205910004748</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2067596664503486</v>
+        <v>-0.2489029380274568</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.437105742472134</v>
+        <v>-1.616918230090987</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.25087240480491</v>
+        <v>2.142984912233598</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.681849119804609</v>
+        <v>-8.787207298747379</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.360062323268985</v>
+        <v>-0.4022055948460932</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.437105742472134</v>
+        <v>-1.616918230090987</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.250770303483326</v>
+        <v>2.142882810912014</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.863718910789643</v>
+        <v>-8.969077089732414</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.4302387236915686</v>
+        <v>-0.4723819952686772</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.618975533457169</v>
+        <v>-1.798788021076022</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.144219944863735</v>
+        <v>2.036332452292423</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.223249233293645</v>
+        <v>-9.328607412236416</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.5687005493951194</v>
+        <v>-0.6108438209722276</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.618975533457169</v>
+        <v>-1.798788021076022</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.149570248161785</v>
+        <v>2.041682755590473</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.273598296747867</v>
+        <v>-9.378956475690638</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.5809241548196304</v>
+        <v>-0.6230674263967386</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.669324596911391</v>
+        <v>-1.849137084530244</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.12727683004643</v>
+        <v>2.019389337475118</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.371217574169263</v>
+        <v>-9.476575753112034</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.6169301151664199</v>
+        <v>-0.6590733867435286</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.766943874332787</v>
+        <v>-1.946756361951641</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.07174701421536</v>
+        <v>1.963859521644048</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.518743662174906</v>
+        <v>-9.624101841117676</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.6730469940471049</v>
+        <v>-0.7151902656242135</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.914469962338431</v>
+        <v>-2.094282449957284</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.986124917733546</v>
+        <v>1.878237425162234</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.72300183750477</v>
+        <v>-9.82836001644754</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.7492370670604083</v>
+        <v>-0.7913803386375164</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.04210890695242</v>
+        <v>-2.221921394571273</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.915054748083795</v>
+        <v>1.807167255512484</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.797334813764934</v>
+        <v>-9.902692992707705</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.7744877030800379</v>
+        <v>-0.8166309746571461</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.186808430887092</v>
+        <v>-2.366620918505946</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.832717588207428</v>
+        <v>1.724830095636116</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.846098735809335</v>
+        <v>-9.829223161040256</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.7786215704043773</v>
+        <v>-0.7718713404967454</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.235572352931494</v>
+        <v>-2.293151086838497</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.818830936474208</v>
+        <v>1.784283696130006</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.02122315319588</v>
+        <v>-10.0043475784268</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8341161166114777</v>
+        <v>-0.8273658867038458</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.410696770318038</v>
+        <v>-2.468275504225041</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.728311506789799</v>
+        <v>1.693764266445597</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.25567524721037</v>
+        <v>-10.23879967244129</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9351161191188697</v>
+        <v>-0.9283658892112379</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.410696770318038</v>
+        <v>-2.468275504225041</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.721092341888202</v>
+        <v>1.686545101544001</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.36004997823681</v>
+        <v>-10.34317440346774</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.9835382023034245</v>
+        <v>-0.9767879723957926</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.515071501344484</v>
+        <v>-2.572650235251487</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.651795312498359</v>
+        <v>1.617248072154157</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.41283613383714</v>
+        <v>-10.39596055906806</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.003536874704999</v>
+        <v>-0.9967866447973668</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.610746987926881</v>
+        <v>-2.668325721833884</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.595505810387477</v>
+        <v>1.560958570043275</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.53887292720543</v>
+        <v>-10.52199735243635</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.0512578634232</v>
+        <v>-1.044507633515568</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.585495365117138</v>
+        <v>-2.643074099024141</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.613350512702437</v>
+        <v>1.578803272358235</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.48685741323662</v>
+        <v>-10.46998183846754</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.026461322149274</v>
+        <v>-1.019711092241642</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.585495365117138</v>
+        <v>-2.643074099024141</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.617340848388838</v>
+        <v>1.582793608044636</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.62852925496074</v>
+        <v>-10.61165368019166</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.084605285737664</v>
+        <v>-1.077855055830032</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.585495365117138</v>
+        <v>-2.643074099024141</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.615865621490096</v>
+        <v>1.581318381145894</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.5789384105359</v>
+        <v>-10.56206283576682</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.049715537802858</v>
+        <v>-1.042965307895226</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.535904520692304</v>
+        <v>-2.593483254599307</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.660673538309869</v>
+        <v>1.626126297965667</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.56613101753113</v>
+        <v>-10.54925544276205</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.057643714247631</v>
+        <v>-1.050893484339999</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.584760295701205</v>
+        <v>-2.642339029608209</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.618308939657845</v>
+        <v>1.583761699313643</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.34028586481172</v>
+        <v>-10.32341029004264</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.9577265801236581</v>
+        <v>-0.9509763502160253</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.542833620114042</v>
+        <v>-2.600412354021045</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.653044018046352</v>
+        <v>1.61849677770215</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.21570720847413</v>
+        <v>-10.19883163370505</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9067559730325621</v>
+        <v>-0.9000057431249302</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.542833620114042</v>
+        <v>-2.600412354021045</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.654183162602411</v>
+        <v>1.619635922258209</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.26860249651841</v>
+        <v>-10.25172692174933</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9252803140881696</v>
+        <v>-0.9185300841805368</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.537878274025596</v>
+        <v>-2.595457007932599</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.659790144417586</v>
+        <v>1.625242904073384</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.19646932123053</v>
+        <v>-10.17959374646145</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8906933397343808</v>
+        <v>-0.8839431098267481</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.537878274025596</v>
+        <v>-2.595457007932599</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.665523848656223</v>
+        <v>1.630976608312021</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.12510292862089</v>
+        <v>-10.1082273538518</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8718840450843865</v>
+        <v>-0.8651338151767547</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.466511881415947</v>
+        <v>-2.524090615322951</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.698606421828146</v>
+        <v>1.664059181483945</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.03164389463566</v>
+        <v>-10.01476831986658</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8443839128032047</v>
+        <v>-0.8376336828955719</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.466511881415947</v>
+        <v>-2.524090615322951</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.688722940515239</v>
+        <v>1.654175700171037</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.764402093767263</v>
+        <v>-9.747526518998182</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.739321752955219</v>
+        <v>-0.7325715230475867</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.466511881415947</v>
+        <v>-2.524090615322951</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.686888380015865</v>
+        <v>1.652341139671663</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.666495055090772</v>
+        <v>-9.649619480321691</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7004592524580837</v>
+        <v>-0.6937090225504514</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.398526131555391</v>
+        <v>-2.456104865462394</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.727379514958738</v>
+        <v>1.692832274614536</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.642541514114814</v>
+        <v>-9.625665939345733</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6902093299222067</v>
+        <v>-0.6834591000145744</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.374572590579433</v>
+        <v>-2.432151324486437</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.742420145689806</v>
+        <v>1.707872905345605</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.378481575792017</v>
+        <v>-9.361606001022936</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5978456707548405</v>
+        <v>-0.5910954408472078</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.110512652256638</v>
+        <v>-2.168091386163641</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.887595792521732</v>
+        <v>1.85304855217753</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.67140195228718</v>
+        <v>-8.654526377518099</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3178008550132061</v>
+        <v>-0.3110506251055738</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.110512652256638</v>
+        <v>-2.168091386163641</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.884808758861431</v>
+        <v>1.850261518517229</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.63121765392099</v>
+        <v>-8.614342079151909</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3013835117788886</v>
+        <v>-0.2946332818712563</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.070328353890447</v>
+        <v>-2.12790708779745</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.909262961768987</v>
+        <v>1.874715721424785</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.467817782981626</v>
+        <v>-8.450942208212545</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2366567421823866</v>
+        <v>-0.2299065122747539</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.906928482951084</v>
+        <v>-1.964507216858087</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.006669705553361</v>
+        <v>1.972122465209159</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.234336560752027</v>
+        <v>-8.217460985982946</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1353398244526942</v>
+        <v>-0.1285895945450619</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.673447260721486</v>
+        <v>-1.731025994628489</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.154682867728973</v>
+        <v>2.120135627384771</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785787</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.084670169744513</v>
+        <v>-8.067794594975432</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.07836547836264796</v>
+        <v>-0.07161524845501521</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.58054376947895</v>
+        <v>-1.638122503385953</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.207532752161535</v>
+        <v>2.172985511817333</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.952394696113626</v>
+        <v>-7.935519121344545</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.03008780216326601</v>
+        <v>-0.02333757225563371</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.448268295848063</v>
+        <v>-1.505847029755066</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.282265523087094</v>
+        <v>2.247718282742892</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.784718794105953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.761795021440474</v>
+        <v>-7.744919446671393</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.04896712839363149</v>
+        <v>0.05571735830126379</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.25766862117491</v>
+        <v>-1.315247355081913</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.399440388578622</v>
+        <v>2.364893148234421</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.512795222756893</v>
+        <v>-7.495919647987812</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1614733890907227</v>
+        <v>0.168223618998355</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.25766862117491</v>
+        <v>-1.315247355081913</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.412346729802281</v>
+        <v>2.377799489458079</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607645</v>
+        <v>3.692931855607647</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.618385212529997</v>
+        <v>-7.601509637760916</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.008738536417737919</v>
+        <v>-0.001988306510105176</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.363258610948014</v>
+        <v>-1.420837344855018</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.2210168063392</v>
+        <v>2.186469565994998</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987904</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.637120114648594</v>
+        <v>-7.620244539879513</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.03231184461190972</v>
+        <v>0.03906207451954202</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.368854620608146</v>
+        <v>-1.426433354515149</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.266203542420207</v>
+        <v>2.231656302076006</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.489180073240995</v>
+        <v>-7.472304498471914</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.02839106151321813</v>
+        <v>-0.02164083160558583</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.348533704699588</v>
+        <v>-1.406112438606591</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.158517169277175</v>
+        <v>2.123969928932973</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409206</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.436210550987006</v>
+        <v>-7.419334976217925</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.01591723886510099</v>
+        <v>-0.009167008957468248</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.295564182445599</v>
+        <v>-1.353142916352602</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.18158489637609</v>
+        <v>2.147037656031888</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.392662144216316</v>
+        <v>-7.375786569447235</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.00545848825191797</v>
+        <v>0.001291741655714773</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.295564182445599</v>
+        <v>-1.353142916352602</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.174624284280997</v>
+        <v>2.140077043936795</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.150513750762458</v>
+        <v>-7.133638175993377</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1058632235107684</v>
+        <v>0.1126134534184011</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.295564182445599</v>
+        <v>-1.353142916352602</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.18908663866214</v>
+        <v>2.154539398317938</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.042254613639936</v>
+        <v>-7.025379038870855</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1436989988189721</v>
+        <v>0.1504492287266048</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.295564182445599</v>
+        <v>-1.353142916352602</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.183618759121335</v>
+        <v>2.149071518777133</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.918963478822805</v>
+        <v>-6.902087904053724</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1905135467564016</v>
+        <v>0.1972637766640339</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.172273047628469</v>
+        <v>-1.229851781535472</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.25509153402219</v>
+        <v>2.220544293677988</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.897814279919362</v>
+        <v>-6.880938705150281</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.206674204555104</v>
+        <v>0.2134244344627363</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.151123848725025</v>
+        <v>-1.208702582632029</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.275482031601581</v>
+        <v>2.240934791257379</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318092</v>
+        <v>3.748328408318094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.654048837935918</v>
+        <v>-6.637173263166837</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2999610896955325</v>
+        <v>0.3067113196031648</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.151123848725025</v>
+        <v>-1.208702582632029</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.271262739948632</v>
+        <v>2.23671549960443</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.552286017658623</v>
+        <v>-6.535410442889542</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3427905317264663</v>
+        <v>0.3495407616340986</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.137904780332597</v>
+        <v>-1.1954835142396</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.281318494904105</v>
+        <v>2.246771254559903</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.302435623709548</v>
+        <v>-6.285560048940467</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4354727642897984</v>
+        <v>0.4422229941974307</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.137904780332597</v>
+        <v>-1.1954835142396</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.274060569887807</v>
+        <v>2.239513329543605</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011498</v>
+        <v>3.8359579870115</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.126543531242115</v>
+        <v>-6.109667956473034</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5094287247974201</v>
+        <v>0.5161789547050528</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.137904780332597</v>
+        <v>-1.1954835142396</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.277659693408456</v>
+        <v>2.243112453064254</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392986</v>
+        <v>3.780933911392988</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.955097068219652</v>
+        <v>-5.938221493450571</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5913348160609595</v>
+        <v>0.5980850459685918</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.9664583173101337</v>
+        <v>-1.024037051217137</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.393855077276487</v>
+        <v>2.359307836932286</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.880807502481312</v>
+        <v>-5.863931927712231</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6200711199725921</v>
+        <v>0.6268213498802244</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.8921687515717944</v>
+        <v>-0.9497474854787973</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.437449294335788</v>
+        <v>2.402902053991586</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.817171760247378</v>
+        <v>-5.800296185478297</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.650220217920483</v>
+        <v>0.6569704478281153</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8285330093378599</v>
+        <v>-0.8861117432448627</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.480325540730466</v>
+        <v>2.445778300386264</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074783</v>
+        <v>3.798814771074785</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.705745000921458</v>
+        <v>-5.688869426152377</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6759851804346466</v>
+        <v>0.6827354103422794</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8285330093378599</v>
+        <v>-0.8861117432448627</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.461519799514261</v>
+        <v>2.42697255917006</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.797694884242296</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.465314504116598</v>
+        <v>-5.448438929347517</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7739004557814684</v>
+        <v>0.7806506856891007</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5881025125329996</v>
+        <v>-0.6456812464400025</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.607521174222055</v>
+        <v>2.572973933877853</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367685</v>
+        <v>3.821593509367687</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.393071935945403</v>
+        <v>-5.376196361176322</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8067267968847665</v>
+        <v>0.8134770267923987</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5881025125329996</v>
+        <v>-0.6456812464400025</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.611450488056875</v>
+        <v>2.576903247712674</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879967</v>
+        <v>3.822326997879968</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.340073613664015</v>
+        <v>-5.323198038894934</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8286047097146616</v>
+        <v>0.8353549396222939</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5327662535310608</v>
+        <v>-0.5903449874380636</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.645330827375378</v>
+        <v>2.610783587031177</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861662650234</v>
+        <v>3.848616626502341</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.231268728184288</v>
+        <v>-5.214393153415207</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8691247351265456</v>
+        <v>0.8758749650341784</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5327662535310608</v>
+        <v>-0.5903449874380636</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.642328898595372</v>
+        <v>2.607781658251171</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675941</v>
+        <v>3.818668951675943</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.011247930147277</v>
+        <v>-4.994372355378196</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.958712091351964</v>
+        <v>0.9654623212595965</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.3915464084630805</v>
+        <v>-0.4491251423700834</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.728639842646774</v>
+        <v>2.694092602302573</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539952</v>
+        <v>3.843274527539954</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.878380241084</v>
+        <v>-4.861504666314919</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.027753349779098</v>
+        <v>1.034503579686731</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.3915464084630805</v>
+        <v>-0.4491251423700834</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.744534025448598</v>
+        <v>2.709986785104396</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496261</v>
+        <v>3.845047386496263</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.758207157719501</v>
+        <v>-4.74133158295042</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.0769684275652</v>
+        <v>1.083718657472832</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.2713733250985816</v>
+        <v>-0.3289520590055844</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.817783719907599</v>
+        <v>2.783236479563397</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.613535012619764</v>
+        <v>-4.596659437850683</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.144925388166535</v>
+        <v>1.151675618074167</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1267011799988442</v>
+        <v>-0.184279913905847</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.914675109528881</v>
+        <v>2.88012786918468</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942103</v>
+        <v>3.735839222942105</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.673409839977456</v>
+        <v>-4.656534265208375</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.107012948624884</v>
+        <v>1.113763178532516</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.1865760073565363</v>
+        <v>-0.2441547412635391</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.864787704515692</v>
+        <v>2.83024046417149</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674515</v>
+        <v>3.762647477674517</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.586610342198448</v>
+        <v>-4.569734767429367</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.164133241059053</v>
+        <v>1.170883470966686</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.1865760073565363</v>
+        <v>-0.2441547412635391</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.887188197838258</v>
+        <v>2.852640957494056</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430695</v>
+        <v>3.729146398430697</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.589080048660254</v>
+        <v>-4.572204473891173</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.163217759847743</v>
+        <v>1.169967989755375</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.1890457138183425</v>
+        <v>-0.2466244477253453</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.885778775334586</v>
+        <v>2.851231534990385</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.743220196003604</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.657450234984264</v>
+        <v>-4.640574660215183</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.146876607792841</v>
+        <v>1.153626837700473</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.1797700147821275</v>
+        <v>-0.2373487486891304</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.902351117231017</v>
+        <v>2.867803876886815</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.71417913950837</v>
+        <v>3.714179139508372</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.765988415900398</v>
+        <v>-4.749112841131317</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.093898044058278</v>
+        <v>1.100648273965911</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.1797700147821275</v>
+        <v>-0.2373487486891304</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.892787825862909</v>
+        <v>2.858240585518707</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417705</v>
+        <v>3.710906731417706</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.796981575229103</v>
+        <v>-4.780106000460022</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.906210345367183</v>
+        <v>0.9129605752748156</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.1797700147821275</v>
+        <v>-0.2373487486891304</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.717497390903295</v>
+        <v>2.682950150559094</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205901</v>
+        <v>3.746042526205903</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.621507315436634</v>
+        <v>-4.604631740667553</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9809672812759584</v>
+        <v>0.9877175111835907</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.1797700147821275</v>
+        <v>-0.2373487486891304</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.722064622895083</v>
+        <v>2.687517382550881</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225446</v>
+        <v>3.765024323225448</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.732443568077883</v>
+        <v>-4.715567993308802</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.912334808980666</v>
+        <v>0.9190850388882983</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.1797700147821275</v>
+        <v>-0.2373487486891304</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.69780665165629</v>
+        <v>2.663259411312088</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111295</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.698780022605601</v>
+        <v>-4.68190444783652</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9289316123894844</v>
+        <v>0.9356818422971167</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.1461064693098457</v>
+        <v>-0.2036852032168485</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.721136164159565</v>
+        <v>2.686588923815363</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.638927403401878</v>
+        <v>-4.622051828632797</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.963045046503106</v>
+        <v>0.9697952764107383</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.1461064693098457</v>
+        <v>-0.2036852032168485</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.731308550591697</v>
+        <v>2.696761310247496</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.5526839403755</v>
+        <v>-4.535808365606419</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9924887022875173</v>
+        <v>0.9992389321951498</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.1461064693098457</v>
+        <v>-0.2036852032168485</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.726254821165558</v>
+        <v>2.691707580821356</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316048</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.59799075977448</v>
+        <v>-4.581115185005399</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9661417499724509</v>
+        <v>0.9728919798800835</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.1869166323190765</v>
+        <v>-0.2444953662260793</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.693544498804544</v>
+        <v>2.658997258460343</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.627023864476781</v>
+        <v>-4.6101482897077</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.955080381124632</v>
+        <v>0.9618306110322645</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.1869166323190765</v>
+        <v>-0.2444953662260793</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.694096371837646</v>
+        <v>2.659549131493445</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.534213383025921</v>
+        <v>-4.517337808256841</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9214772655963417</v>
+        <v>0.928227495503974</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.09410615086821711</v>
+        <v>-0.15168488477522</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.679055352599527</v>
+        <v>2.644508112255326</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.578602852355349</v>
+        <v>-4.561727277586268</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9055949537891714</v>
+        <v>0.9123451836968037</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1384956201976448</v>
+        <v>-0.1960743541046476</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.654295146926472</v>
+        <v>2.61974790658227</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.465931634119099</v>
+        <v>-4.449056059350018</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9457391495953944</v>
+        <v>0.9524893795030269</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.02582440196139457</v>
+        <v>-0.08340313586839743</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.716973586379945</v>
+        <v>2.682426346035743</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.353554632936426</v>
+        <v>-4.336679058167345</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9961812458991308</v>
+        <v>1.002931475806763</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.02582440196139457</v>
+        <v>-0.08340313586839743</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.722464882210612</v>
+        <v>2.68791764186641</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.381335030837779</v>
+        <v>-4.364459456068698</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9965662885071289</v>
+        <v>1.003316518414761</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.05360479986274763</v>
+        <v>-0.1111835337697505</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.71729384523834</v>
+        <v>2.682746604894138</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.643069621705327</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.464336311863057</v>
+        <v>-4.447460737093976</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8017214960976706</v>
+        <v>0.8084717260053029</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.07217568438992139</v>
+        <v>-0.1297544182969242</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.544507034522688</v>
+        <v>2.509959794178487</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>3.682716310729271</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.572950390306389</v>
+        <v>-4.556074815537308</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8784255254395439</v>
+        <v>0.8851757553471762</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.07217568438992139</v>
+        <v>-0.1297544182969242</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.664656695241894</v>
+        <v>2.630109454897692</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190769</v>
+        <v>3.733012441190771</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.659548973287492</v>
+        <v>-4.642673398518411</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8582991183494255</v>
+        <v>0.865049348257058</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.07217568438992139</v>
+        <v>-0.1297544182969242</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.679169721344217</v>
+        <v>2.644622481000015</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913426</v>
+        <v>3.741174069913428</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.62116531072934</v>
+        <v>-4.604289735960259</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8710720247150547</v>
+        <v>0.877822254622687</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.03379202183177021</v>
+        <v>-0.09137075573877307</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.699619360221476</v>
+        <v>2.665072119877275</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532487</v>
+        <v>3.751147197532489</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.444048980694174</v>
+        <v>-4.427173405925093</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9386475855744232</v>
+        <v>0.9453978154820555</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.03379202183177021</v>
+        <v>-0.09137075573877307</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.696348389066778</v>
+        <v>2.661801148722577</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793906</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.48914122552772</v>
+        <v>-4.472265650758639</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9212940794029179</v>
+        <v>0.9280443093105504</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.09568806500116001</v>
+        <v>-0.1532667989081629</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.659894154927057</v>
+        <v>2.625346914582856</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011237</v>
+        <v>3.750729377011239</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.309765804288952</v>
+        <v>-4.292890229519871</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9868312232048393</v>
+        <v>0.9935814531124718</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.06108869316955867</v>
+        <v>0.003509959262555817</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.747747185135903</v>
+        <v>2.713199944791701</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982231</v>
+        <v>3.716991718982233</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.354780017809558</v>
+        <v>-4.337904443040477</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9496329931281868</v>
+        <v>0.9563832230358191</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.03073979785495407</v>
+        <v>-0.02683893605204879</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.71034530327873</v>
+        <v>2.675798062934528</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509541</v>
+        <v>3.737026608509542</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.621784528081993</v>
+        <v>-4.604908953312912</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8485227513581586</v>
+        <v>0.8552729812657909</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.1636232401879945</v>
+        <v>-0.2212019740949974</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.599419042791907</v>
+        <v>2.564871802447705</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760811</v>
+        <v>3.702309454760813</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.722982309519166</v>
+        <v>-4.706106734750085</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8072475606797909</v>
+        <v>0.8139977905874232</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2320320537333137</v>
+        <v>-0.2896107876403166</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.557577676561217</v>
+        <v>2.523030436217015</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815456</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.690506723348394</v>
+        <v>-4.673631148579313</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8178377567024164</v>
+        <v>0.824587986610049</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2320320537333137</v>
+        <v>-0.2896107876403166</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.555177638115533</v>
+        <v>2.520630397771332</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378101</v>
+        <v>3.709510443378103</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.671468595641096</v>
+        <v>-4.654593020872015</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8219777269935804</v>
+        <v>0.8287279569012127</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.2902156650645082</v>
+        <v>-0.3477943989715111</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.516792190525062</v>
+        <v>2.48224495018086</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131253</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.702595226791715</v>
+        <v>-4.685719652022634</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9871089434720135</v>
+        <v>0.9938591733796458</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.2902156650645082</v>
+        <v>-0.3477943989715111</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.694374059463742</v>
+        <v>2.65982681911954</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067867</v>
+        <v>3.722447362067869</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.716461988125633</v>
+        <v>-4.699586413356552</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9823955679245799</v>
+        <v>0.9891457978322122</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3280735817983312</v>
+        <v>-0.385652315705334</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.672492638409582</v>
+        <v>2.63794539806538</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789124</v>
+        <v>3.787425580789126</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.736719286654591</v>
+        <v>-4.71984371188551</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9803011789099227</v>
+        <v>0.987051408817555</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.3280735817983312</v>
+        <v>-0.385652315705334</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.678501168806508</v>
+        <v>2.643953928462306</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519911</v>
+        <v>3.781501250519913</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.588976316419588</v>
+        <v>-4.572100741650507</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.118551014795946</v>
+        <v>1.125301244703578</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.160266224563448</v>
+        <v>-0.2178449584704509</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.858338230939459</v>
+        <v>2.823790990595258</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181173</v>
+        <v>3.802245929181175</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.690990998950809</v>
+        <v>-4.674115424181728</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.080538763314938</v>
+        <v>1.08728899322257</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.160266224563448</v>
+        <v>-0.2178449584704509</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.86113185247094</v>
+        <v>2.826584612126739</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394734</v>
+        <v>3.805608985394736</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.684838292898025</v>
+        <v>-4.667962718128944</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.08366219412771</v>
+        <v>1.090412424035343</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.1541135185106637</v>
+        <v>-0.2116922524176666</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.865485824494269</v>
+        <v>2.830938584150068</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890614</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.701647591048527</v>
+        <v>-4.684772016279446</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.07601895160762</v>
+        <v>1.082769181515252</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.1709228166611654</v>
+        <v>-0.2285015505681682</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.854480722344079</v>
+        <v>2.819933481999877</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798429</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.639349592272405</v>
+        <v>-4.622474017503324</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.167273704914889</v>
+        <v>1.174023934822522</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.1709228166611654</v>
+        <v>-0.2285015505681682</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.9208162761409</v>
+        <v>2.886269035796698</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992194</v>
+        <v>3.848729139992196</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.437559394607247</v>
+        <v>-4.420683819838166</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9565706563703507</v>
+        <v>0.963320886277983</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.02709537550798902</v>
+        <v>-0.03048335839901384</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.748208063831791</v>
+        <v>2.713660823487589</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.377668712964653</v>
+        <v>-4.360793138195572</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.050817161349563</v>
+        <v>1.057567391257196</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.0869860571505825</v>
+        <v>0.02940732324357964</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.854432705139522</v>
+        <v>2.81988546479532</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319549</v>
+        <v>3.81906330031955</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.475409257589628</v>
+        <v>-4.458533682820547</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.026348679615617</v>
+        <v>1.033098909523249</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.07109677901760231</v>
+        <v>0.01351804511059945</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.859526874375777</v>
+        <v>2.824979634031576</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489388</v>
+        <v>3.83181903248939</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.651747017712557</v>
+        <v>-4.634871442943476</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9543495563911171</v>
+        <v>0.9610997862987494</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.1052409811053271</v>
+        <v>-0.1628197150123299</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.752260199126691</v>
+        <v>2.71771295878249</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397798</v>
+        <v>3.8364116723978</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.57532497128063</v>
+        <v>-4.558449396511549</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9834099930038163</v>
+        <v>0.9901602229114488</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.1052409811053271</v>
+        <v>-0.1628197150123299</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.75075181716662</v>
+        <v>2.716204576822418</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024966</v>
+        <v>3.836023391024968</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.530951839642062</v>
+        <v>-4.514076264872981</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.00102211309468</v>
+        <v>1.007772343002312</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.06086784946675849</v>
+        <v>-0.1184465833737613</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.777238563585197</v>
+        <v>2.742691323240996</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863226</v>
+        <v>3.821591150863227</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.522997869347289</v>
+        <v>-4.506122294578208</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.004203701212589</v>
+        <v>1.010953931120221</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.06086784946675849</v>
+        <v>-0.1184465833737613</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.777238563585197</v>
+        <v>2.742691323240996</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947585</v>
+        <v>3.833040181947586</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.475342138786234</v>
+        <v>-4.458466564017153</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.029647750464816</v>
+        <v>1.036397980372448</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.01321211890570284</v>
+        <v>-0.0707908528127057</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.812213758949635</v>
+        <v>2.777666518605433</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326877</v>
+        <v>3.822707244326879</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.416567442210528</v>
+        <v>-4.330782254222856</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.058050002469823</v>
+        <v>1.092364077664892</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.04556257767000216</v>
+        <v>0.05689345698159076</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.852370950269783</v>
+        <v>2.859169477856736</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314553</v>
+        <v>3.828837911314555</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.477234032612918</v>
+        <v>-4.391448844625245</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.020538038784739</v>
+        <v>1.054852113979808</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.03613573904853151</v>
+        <v>-0.02480485973694291</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.790106632714535</v>
+        <v>2.796905160301488</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690029</v>
+        <v>3.81686606769003</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.432395631004519</v>
+        <v>-4.346610443016846</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.042571102038727</v>
+        <v>1.076885177233796</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.03159230610366204</v>
+        <v>-0.02026142679207343</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.796930395092085</v>
+        <v>2.803728922679039</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.533154266761517</v>
+        <v>-4.447369078773844</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.006428587367006</v>
+        <v>1.040742662562075</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.1204178748306675</v>
+        <v>-0.1090869955190789</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.74779599348696</v>
+        <v>2.754594521073913</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.488951429675617</v>
+        <v>-4.403166241687944</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.029989324729203</v>
+        <v>1.064303399924272</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.07621503774476701</v>
+        <v>-0.06488415843317841</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.780197298266337</v>
+        <v>2.78699582585329</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.52593045733906</v>
+        <v>-4.440145269351387</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.013607714133074</v>
+        <v>1.047921789328143</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.03924113595343648</v>
+        <v>-0.02791025664184787</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.800791639810383</v>
+        <v>2.807590167397336</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.5459885362039</v>
+        <v>-4.460203348216227</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.056832247770177</v>
+        <v>1.091146322965246</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.03924113595343648</v>
+        <v>-0.02791025664184787</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.852039404993423</v>
+        <v>2.858837932580376</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.50605786302601</v>
+        <v>-4.420272675038337</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.071245221635586</v>
+        <v>1.105559296830656</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.0006895372244538622</v>
+        <v>0.01202041653604247</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.87443851349441</v>
+        <v>2.881237041081363</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.455025770303482</v>
+        <v>-4.369240582315809</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.086606286962867</v>
+        <v>1.120920362157937</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.05172162994698182</v>
+        <v>0.06305250925857042</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.900005997366197</v>
+        <v>2.90680452495315</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.389801589176277</v>
+        <v>-4.304016401188604</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.129883363506454</v>
+        <v>1.164197438701524</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.1169458110741874</v>
+        <v>0.128276690385776</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.956327910135225</v>
+        <v>2.963126437722178</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.352374569105143</v>
+        <v>-4.26658938111747</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.140815143834188</v>
+        <v>1.175129219029258</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.1221973491033691</v>
+        <v>0.1335282284149577</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.955439805252015</v>
+        <v>2.962238332838968</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.372486225139851</v>
+        <v>-4.286701037152178</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.134027273751546</v>
+        <v>1.168341348946615</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.1332246941007883</v>
+        <v>0.1445555734123769</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.963313004581706</v>
+        <v>2.97011153216866</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.318741410712646</v>
+        <v>-4.232956222724973</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.316082970543638</v>
+        <v>1.350397045738707</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.1432880035412503</v>
+        <v>0.1546188828528389</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.129908761267195</v>
+        <v>3.136707288854148</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.294949842106504</v>
+        <v>-4.209164654118831</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.445712507203912</v>
+        <v>1.480026582398981</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.1670795721473926</v>
+        <v>0.1784104514589812</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.264296611648697</v>
+        <v>3.27109513923565</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.268865757842696</v>
+        <v>-4.183080569855023</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.447854116923295</v>
+        <v>1.482168192118364</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.1670795721473926</v>
+        <v>0.1784104514589812</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.256004587662556</v>
+        <v>3.262803115249509</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.264531454785648</v>
+        <v>-4.178746266797975</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.447781033729893</v>
+        <v>1.482095108924962</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.3187296754665965</v>
+        <v>0.3300605547781851</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.345187845237858</v>
+        <v>3.351986372824811</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.255638993392365</v>
+        <v>-4.169853805404692</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.468892424013998</v>
+        <v>1.503206499209067</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.3187296754665965</v>
+        <v>0.3300605547781851</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.362742250964649</v>
+        <v>3.369540778551603</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.424115110362242</v>
+        <v>-4.338329922374569</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.393357024630631</v>
+        <v>1.4276710998257</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.2907818397500157</v>
+        <v>0.3021127190616043</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.337828596939285</v>
+        <v>3.344627124526238</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.233772154546119</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.726315581500659</v>
+        <v>-3.640530393512986</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.742889497632108</v>
+        <v>1.777203572827177</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.220433780379605</v>
+        <v>0.2317646596911936</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.366032422773882</v>
+        <v>3.372830950360835</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.224436177043023</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.703594477817507</v>
+        <v>-3.617809289829834</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.742641961602273</v>
+        <v>1.776956036797342</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.220433780379605</v>
+        <v>0.2317646596911936</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.356696445270786</v>
+        <v>3.363494972857739</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.383342302894192</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.843887077354699</v>
+        <v>-3.758101889367026</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.845431047638565</v>
+        <v>1.879745122833635</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.08014118084241234</v>
+        <v>0.09147206015400094</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.43142701139964</v>
+        <v>3.438225538986593</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.420420125387839</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.998668084132954</v>
+        <v>-3.912882896145281</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.82059646742091</v>
+        <v>1.854910542615979</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.04677350678793624</v>
+        <v>0.05810438609952484</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.448484229460601</v>
+        <v>3.455282757047554</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.417095481377384</v>
       </c>
       <c r="D2001" t="n">
-        <v>-4.234778905308041</v>
+        <v>-3.980143340167198</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.72282749494042</v>
+        <v>1.824681720996757</v>
       </c>
       <c r="F2001" t="n">
-        <v>-0.1893373143871505</v>
+        <v>-0.009156057922392269</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.303493092745094</v>
+        <v>3.411601846623949</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.451087042262799</v>
+        <v>3.80993964778956</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.266584865068838</v>
+        <v>3.427101635022126</v>
       </c>
       <c r="D2002" t="n">
-        <v>-4.157600945643908</v>
+        <v>-4.06170920899944</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.603188062497528</v>
+        <v>1.802061527108602</v>
       </c>
       <c r="F2002" t="n">
-        <v>-0.1121593547230164</v>
+        <v>-0.09072192675463381</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.199289252235029</v>
+        <v>3.372668478969346</v>
       </c>
     </row>
   </sheetData>
